--- a/InputData/elec/SoESCaOMCbIC/Share of Electricity Sector Capital and OM Costs by ISIC Code.xlsx
+++ b/InputData/elec/SoESCaOMCbIC/Share of Electricity Sector Capital and OM Costs by ISIC Code.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\SoESCaOMCbIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\SoESCaOMCbIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F8CB7E-4F9B-4533-81A3-FD34044A8A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36B3B44-873D-4041-9BDC-E6592614157F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -2366,6 +2366,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2389,9 +2392,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3590,14 +3590,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="134" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="136"/>
+      <c r="A1" s="135" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="137"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3919,14 +3919,14 @@
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="130" t="s">
+      <c r="A18" s="131" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="131"/>
-      <c r="C18" s="131"/>
-      <c r="D18" s="132"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="133"/>
+      <c r="B18" s="132"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="134"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="92" t="s">
@@ -4834,14 +4834,14 @@
     </row>
     <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="75" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A75" s="134" t="s">
+      <c r="A75" s="135" t="s">
         <v>12</v>
       </c>
-      <c r="B75" s="135"/>
-      <c r="C75" s="135"/>
-      <c r="D75" s="137"/>
-      <c r="E75" s="137"/>
-      <c r="F75" s="136"/>
+      <c r="B75" s="136"/>
+      <c r="C75" s="136"/>
+      <c r="D75" s="138"/>
+      <c r="E75" s="138"/>
+      <c r="F75" s="137"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
@@ -5443,14 +5443,14 @@
     </row>
     <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="110" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A110" s="134" t="s">
+      <c r="A110" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="B110" s="135"/>
-      <c r="C110" s="135"/>
-      <c r="D110" s="137"/>
-      <c r="E110" s="137"/>
-      <c r="F110" s="136"/>
+      <c r="B110" s="136"/>
+      <c r="C110" s="136"/>
+      <c r="D110" s="138"/>
+      <c r="E110" s="138"/>
+      <c r="F110" s="137"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
@@ -6044,14 +6044,14 @@
     </row>
     <row r="144" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="145" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A145" s="130" t="s">
+      <c r="A145" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="B145" s="131"/>
-      <c r="C145" s="131"/>
-      <c r="D145" s="132"/>
-      <c r="E145" s="132"/>
-      <c r="F145" s="133"/>
+      <c r="B145" s="132"/>
+      <c r="C145" s="132"/>
+      <c r="D145" s="133"/>
+      <c r="E145" s="133"/>
+      <c r="F145" s="134"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
@@ -6370,14 +6370,14 @@
     </row>
     <row r="163" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="164" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A164" s="130" t="s">
+      <c r="A164" s="131" t="s">
         <v>71</v>
       </c>
-      <c r="B164" s="131"/>
-      <c r="C164" s="131"/>
-      <c r="D164" s="132"/>
-      <c r="E164" s="132"/>
-      <c r="F164" s="133"/>
+      <c r="B164" s="132"/>
+      <c r="C164" s="132"/>
+      <c r="D164" s="133"/>
+      <c r="E164" s="133"/>
+      <c r="F164" s="134"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
@@ -7356,14 +7356,14 @@
     </row>
     <row r="218" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="219" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A219" s="130" t="s">
+      <c r="A219" s="131" t="s">
         <v>226</v>
       </c>
-      <c r="B219" s="131"/>
-      <c r="C219" s="131"/>
-      <c r="D219" s="132"/>
-      <c r="E219" s="132"/>
-      <c r="F219" s="133"/>
+      <c r="B219" s="132"/>
+      <c r="C219" s="132"/>
+      <c r="D219" s="133"/>
+      <c r="E219" s="133"/>
+      <c r="F219" s="134"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
@@ -7639,14 +7639,14 @@
     </row>
     <row r="234" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="235" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A235" s="130" t="s">
+      <c r="A235" s="131" t="s">
         <v>227</v>
       </c>
-      <c r="B235" s="131"/>
-      <c r="C235" s="131"/>
-      <c r="D235" s="132"/>
-      <c r="E235" s="132"/>
-      <c r="F235" s="133"/>
+      <c r="B235" s="132"/>
+      <c r="C235" s="132"/>
+      <c r="D235" s="133"/>
+      <c r="E235" s="133"/>
+      <c r="F235" s="134"/>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
@@ -8603,14 +8603,14 @@
       <c r="F288" s="10"/>
     </row>
     <row r="289" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A289" s="130" t="s">
+      <c r="A289" s="131" t="s">
         <v>337</v>
       </c>
-      <c r="B289" s="131"/>
-      <c r="C289" s="131"/>
-      <c r="D289" s="132"/>
-      <c r="E289" s="132"/>
-      <c r="F289" s="133"/>
+      <c r="B289" s="132"/>
+      <c r="C289" s="132"/>
+      <c r="D289" s="133"/>
+      <c r="E289" s="133"/>
+      <c r="F289" s="134"/>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="92" t="s">
@@ -9086,14 +9086,14 @@
       <c r="D314" s="101"/>
     </row>
     <row r="315" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A315" s="130" t="s">
+      <c r="A315" s="131" t="s">
         <v>365</v>
       </c>
-      <c r="B315" s="131"/>
-      <c r="C315" s="131"/>
-      <c r="D315" s="132"/>
-      <c r="E315" s="132"/>
-      <c r="F315" s="133"/>
+      <c r="B315" s="132"/>
+      <c r="C315" s="132"/>
+      <c r="D315" s="133"/>
+      <c r="E315" s="133"/>
+      <c r="F315" s="134"/>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="92" t="s">
@@ -19662,7 +19662,7 @@
       </c>
     </row>
     <row r="24" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A24" s="138" t="s">
+      <c r="A24" s="130" t="s">
         <v>511</v>
       </c>
       <c r="B24" s="77">
@@ -19835,7 +19835,7 @@
       </c>
     </row>
     <row r="25" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A25" s="138" t="s">
+      <c r="A25" s="130" t="s">
         <v>512</v>
       </c>
       <c r="B25" s="77">
@@ -23982,7 +23982,7 @@
       </c>
     </row>
     <row r="24" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A24" s="138" t="s">
+      <c r="A24" s="130" t="s">
         <v>511</v>
       </c>
       <c r="B24" s="77">
@@ -24155,7 +24155,7 @@
       </c>
     </row>
     <row r="25" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A25" s="138" t="s">
+      <c r="A25" s="130" t="s">
         <v>512</v>
       </c>
       <c r="B25" s="77">
@@ -26628,7 +26628,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="89">
         <v>0</v>
@@ -26655,7 +26655,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="89">
         <v>0</v>
@@ -28133,7 +28133,7 @@
       </c>
     </row>
     <row r="24" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A24" s="138" t="s">
+      <c r="A24" s="130" t="s">
         <v>511</v>
       </c>
       <c r="B24" s="77">
@@ -28306,7 +28306,7 @@
       </c>
     </row>
     <row r="25" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A25" s="138" t="s">
+      <c r="A25" s="130" t="s">
         <v>512</v>
       </c>
       <c r="B25" s="77">

--- a/InputData/elec/SoESCaOMCbIC/Share of Electricity Sector Capital and OM Costs by ISIC Code.xlsx
+++ b/InputData/elec/SoESCaOMCbIC/Share of Electricity Sector Capital and OM Costs by ISIC Code.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\SoESCaOMCbIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\elec\SoESCaOMCbIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36B3B44-873D-4041-9BDC-E6592614157F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9680A139-0A6F-4C1C-A62D-09CEA4056454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="59445" yWindow="1200" windowWidth="24555" windowHeight="14835" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -2847,22 +2847,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="61.85546875" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" customWidth="1"/>
-    <col min="4" max="4" width="65.7109375" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
-    <col min="6" max="6" width="63.42578125" customWidth="1"/>
-    <col min="8" max="8" width="52.85546875" customWidth="1"/>
+    <col min="2" max="2" width="61.81640625" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" customWidth="1"/>
+    <col min="4" max="4" width="65.7265625" customWidth="1"/>
+    <col min="5" max="5" width="5.7265625" customWidth="1"/>
+    <col min="6" max="6" width="63.453125" customWidth="1"/>
+    <col min="8" max="8" width="52.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="71" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="71" t="s">
         <v>214</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>215</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B5" s="79">
         <v>2022</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>449</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B7" s="65" t="s">
         <v>448</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>450</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B10" s="78" t="s">
         <v>327</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>215</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B12" s="79">
         <v>2019</v>
       </c>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H12" s="79"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>287</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B14" s="65" t="s">
         <v>286</v>
       </c>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H14" s="65"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>288</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="78" t="s">
         <v>223</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>215</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="79">
         <v>2016</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" ht="29" x14ac:dyDescent="0.35">
       <c r="B20" s="107" t="s">
         <v>224</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" ht="29" x14ac:dyDescent="0.35">
       <c r="B21" s="109" t="s">
         <v>114</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>330</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="78" t="s">
         <v>328</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>215</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="79">
         <v>2016</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>329</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="65" t="s">
         <v>255</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>288</v>
       </c>
@@ -3159,37 +3159,37 @@
         <v>288</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="71" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>355</v>
       </c>
@@ -3215,19 +3215,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="77.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="77.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7265625" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.54296875" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="71" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="71" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="71" t="s">
         <v>194</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>429</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>430</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>447</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>125</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>126</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>127</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>128</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>129</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>428</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>427</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>130</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>440</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>441</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>442</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>443</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>131</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>132</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>133</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>134</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>135</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>136</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>137</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>444</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>445</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>446</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>138</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>139</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>140</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>141</v>
       </c>
@@ -3483,7 +3483,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>142</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>143</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>144</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>145</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>146</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>147</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>148</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>149</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>150</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>151</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>152</v>
       </c>
@@ -3579,17 +3579,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F381"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="65.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.140625" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.5703125" customWidth="1"/>
-    <col min="6" max="6" width="60.42578125" customWidth="1"/>
+    <col min="1" max="1" width="65.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.1796875" customWidth="1"/>
+    <col min="4" max="4" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.54296875" customWidth="1"/>
+    <col min="6" max="6" width="60.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="135" t="s">
         <v>0</v>
       </c>
@@ -3599,7 +3599,7 @@
       <c r="E1" s="136"/>
       <c r="F1" s="137"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -3631,7 +3631,7 @@
       <c r="E3" s="21"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>153</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>154</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>155</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>156</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>157</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>158</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>159</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>160</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="57" t="s">
         <v>161</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="88" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>8</v>
       </c>
@@ -3871,7 +3871,7 @@
       <c r="E14" s="13"/>
       <c r="F14" s="14"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>257</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="87" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" s="87" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="17" t="s">
         <v>258</v>
       </c>
@@ -3917,8 +3917,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="1:6" ht="19" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A18" s="131" t="s">
         <v>9</v>
       </c>
@@ -3928,7 +3928,7 @@
       <c r="E18" s="133"/>
       <c r="F18" s="134"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="92" t="s">
         <v>1</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>6</v>
       </c>
@@ -3960,7 +3960,7 @@
       <c r="E20" s="21"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="20" t="s">
         <v>237</v>
       </c>
@@ -3970,7 +3970,7 @@
       <c r="E21" s="90"/>
       <c r="F21" s="56"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="20" t="s">
         <v>259</v>
       </c>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="F22" s="16"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="20" t="s">
         <v>260</v>
       </c>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="F23" s="16"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="20" t="s">
         <v>261</v>
       </c>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="F24" s="16"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="20" t="s">
         <v>262</v>
       </c>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="F25" s="16"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="20" t="s">
         <v>263</v>
       </c>
@@ -4062,7 +4062,7 @@
       <c r="E26" s="90"/>
       <c r="F26" s="16"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="20" t="s">
         <v>118</v>
       </c>
@@ -4072,7 +4072,7 @@
       <c r="E27" s="90"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="20" t="s">
         <v>228</v>
       </c>
@@ -4082,7 +4082,7 @@
       <c r="E28" s="90"/>
       <c r="F28" s="16"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="20" t="s">
         <v>264</v>
       </c>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="F29" s="16"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="20" t="s">
         <v>265</v>
       </c>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F30" s="16"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="20" t="s">
         <v>266</v>
       </c>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="F31" s="16"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="20" t="s">
         <v>267</v>
       </c>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="20" t="s">
         <v>268</v>
       </c>
@@ -4174,7 +4174,7 @@
       <c r="E33" s="90"/>
       <c r="F33" s="16"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="20" t="s">
         <v>231</v>
       </c>
@@ -4184,7 +4184,7 @@
       <c r="E34" s="90"/>
       <c r="F34" s="16"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="20" t="s">
         <v>269</v>
       </c>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="20" t="s">
         <v>270</v>
       </c>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="20" t="s">
         <v>236</v>
       </c>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="20" t="s">
         <v>271</v>
       </c>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="20" t="s">
         <v>272</v>
       </c>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="20" t="s">
         <v>273</v>
       </c>
@@ -4296,7 +4296,7 @@
       <c r="E40" s="21"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="20" t="s">
         <v>274</v>
       </c>
@@ -4306,7 +4306,7 @@
       <c r="E41" s="21"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="20" t="s">
         <v>275</v>
       </c>
@@ -4316,7 +4316,7 @@
       <c r="E42" s="21"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="20" t="s">
         <v>276</v>
       </c>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="20" t="s">
         <v>277</v>
       </c>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="20" t="s">
         <v>278</v>
       </c>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="20" t="s">
         <v>279</v>
       </c>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="20" t="s">
         <v>280</v>
       </c>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="20" t="s">
         <v>281</v>
       </c>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="20" t="s">
         <v>282</v>
       </c>
@@ -4448,7 +4448,7 @@
       <c r="E49" s="21"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="20" t="s">
         <v>283</v>
       </c>
@@ -4460,7 +4460,7 @@
       <c r="E50" s="21"/>
       <c r="F50" s="6"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="20" t="s">
         <v>284</v>
       </c>
@@ -4472,7 +4472,7 @@
       <c r="E51" s="21"/>
       <c r="F51" s="6"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="20" t="s">
         <v>285</v>
       </c>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="F52" s="6"/>
     </row>
-    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="24" t="s">
         <v>11</v>
       </c>
@@ -4504,7 +4504,7 @@
       <c r="E53" s="25"/>
       <c r="F53" s="10"/>
     </row>
-    <row r="54" spans="1:6" s="88" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="11" t="s">
         <v>8</v>
       </c>
@@ -4514,7 +4514,7 @@
       <c r="E54" s="13"/>
       <c r="F54" s="14"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="20" t="s">
         <v>65</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="E55" s="21"/>
       <c r="F55" s="6"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="20" t="s">
         <v>289</v>
       </c>
@@ -4534,7 +4534,7 @@
       <c r="E56" s="21"/>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="20" t="s">
         <v>290</v>
       </c>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="20" t="s">
         <v>291</v>
       </c>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="F58" s="6"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="20" t="s">
         <v>292</v>
       </c>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="F59" s="6"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="20" t="s">
         <v>293</v>
       </c>
@@ -4606,7 +4606,7 @@
       <c r="E60" s="21"/>
       <c r="F60" s="6"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="20" t="s">
         <v>105</v>
       </c>
@@ -4616,7 +4616,7 @@
       <c r="E61" s="21"/>
       <c r="F61" s="6"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="20" t="s">
         <v>294</v>
       </c>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="F62" s="6"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="20" t="s">
         <v>295</v>
       </c>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="20" t="s">
         <v>296</v>
       </c>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="20" t="s">
         <v>297</v>
       </c>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="20" t="s">
         <v>298</v>
       </c>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="20" t="s">
         <v>299</v>
       </c>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="20" t="s">
         <v>300</v>
       </c>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="20" t="s">
         <v>301</v>
       </c>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="20" t="s">
         <v>302</v>
       </c>
@@ -4788,7 +4788,7 @@
       <c r="E70" s="21"/>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="20" t="s">
         <v>50</v>
       </c>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="F71" s="6"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="20" t="s">
         <v>303</v>
       </c>
@@ -4820,7 +4820,7 @@
       <c r="E72" s="21"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="24" t="s">
         <v>304</v>
       </c>
@@ -4832,8 +4832,8 @@
       <c r="E73" s="25"/>
       <c r="F73" s="10"/>
     </row>
-    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="75" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A75" s="135" t="s">
         <v>12</v>
       </c>
@@ -4843,7 +4843,7 @@
       <c r="E75" s="138"/>
       <c r="F75" s="137"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>1</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>6</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>14</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
         <v>16</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>17</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
         <v>18</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="30" t="s">
         <v>19</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
         <v>20</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
         <v>21</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>22</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="30" t="s">
         <v>23</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="30" t="s">
         <v>24</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
         <v>25</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>26</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>27</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>28</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>29</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
         <v>30</v>
       </c>
@@ -5171,7 +5171,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>31</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
         <v>32</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>33</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="30" t="s">
         <v>34</v>
       </c>
@@ -5250,7 +5250,7 @@
       <c r="E97" s="73"/>
       <c r="F97" s="16"/>
     </row>
-    <row r="98" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="31" t="s">
         <v>35</v>
       </c>
@@ -5263,7 +5263,7 @@
       <c r="E98" s="34"/>
       <c r="F98" s="35"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="11" t="s">
         <v>8</v>
       </c>
@@ -5273,7 +5273,7 @@
       <c r="E99" s="37"/>
       <c r="F99" s="14"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="38" t="s">
         <v>20</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="38" t="s">
         <v>36</v>
       </c>
@@ -5317,7 +5317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="38" t="s">
         <v>37</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="40" t="s">
         <v>35</v>
       </c>
@@ -5352,7 +5352,7 @@
       <c r="E103" s="43"/>
       <c r="F103" s="10"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="11" t="s">
         <v>38</v>
       </c>
@@ -5362,7 +5362,7 @@
       <c r="E104" s="37"/>
       <c r="F104" s="14"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="38" t="s">
         <v>39</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="38" t="s">
         <v>40</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="38" t="s">
         <v>29</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="40" t="s">
         <v>35</v>
       </c>
@@ -5441,8 +5441,8 @@
       <c r="E108" s="43"/>
       <c r="F108" s="10"/>
     </row>
-    <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="110" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="110" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A110" s="135" t="s">
         <v>41</v>
       </c>
@@ -5452,7 +5452,7 @@
       <c r="E110" s="138"/>
       <c r="F110" s="137"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>1</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
         <v>6</v>
       </c>
@@ -5484,12 +5484,12 @@
       <c r="E112" s="3"/>
       <c r="F112" s="16"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>16</v>
       </c>
@@ -5511,7 +5511,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>17</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>18</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>43</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>44</v>
       </c>
@@ -5581,7 +5581,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>21</v>
       </c>
@@ -5603,7 +5603,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>45</v>
       </c>
@@ -5625,7 +5625,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>46</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>43</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
         <v>24</v>
       </c>
@@ -5675,7 +5675,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
         <v>25</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>47</v>
       </c>
@@ -5709,7 +5709,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
         <v>27</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>28</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="7" t="s">
         <v>48</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="7" t="s">
         <v>30</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
         <v>33</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
         <v>34</v>
       </c>
@@ -5831,7 +5831,7 @@
       <c r="E131" s="73"/>
       <c r="F131" s="16"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
         <v>49</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="47" t="s">
         <v>50</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="11" t="s">
         <v>8</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="38" t="s">
         <v>20</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="38" t="s">
         <v>36</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="38" t="s">
         <v>37</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="40" t="s">
         <v>35</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="11" t="s">
         <v>38</v>
       </c>
@@ -5963,7 +5963,7 @@
       <c r="E139" s="37"/>
       <c r="F139" s="14"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="38" t="s">
         <v>51</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="38" t="s">
         <v>40</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="38" t="s">
         <v>29</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="40" t="s">
         <v>35</v>
       </c>
@@ -6042,8 +6042,8 @@
       <c r="E143" s="26"/>
       <c r="F143" s="10"/>
     </row>
-    <row r="144" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="145" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="145" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A145" s="131" t="s">
         <v>52</v>
       </c>
@@ -6053,7 +6053,7 @@
       <c r="E145" s="133"/>
       <c r="F145" s="134"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>1</v>
       </c>
@@ -6073,7 +6073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="5" t="s">
         <v>6</v>
       </c>
@@ -6085,7 +6085,7 @@
       <c r="E147" s="3"/>
       <c r="F147" s="16"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="7" t="s">
         <v>53</v>
       </c>
@@ -6095,7 +6095,7 @@
       <c r="E148" s="22"/>
       <c r="F148" s="6"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
         <v>54</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
         <v>57</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="7" t="s">
         <v>58</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
         <v>59</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" s="7" t="s">
         <v>60</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
         <v>61</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" s="7" t="s">
         <v>62</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" s="7" t="s">
         <v>63</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" s="7" t="s">
         <v>64</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="57" t="s">
         <v>11</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" s="11" t="s">
         <v>8</v>
       </c>
@@ -6314,7 +6314,7 @@
       <c r="E159" s="60"/>
       <c r="F159" s="14"/>
     </row>
-    <row r="160" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="57" t="s">
         <v>65</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" s="11" t="s">
         <v>38</v>
       </c>
@@ -6346,7 +6346,7 @@
       <c r="E161" s="60"/>
       <c r="F161" s="14"/>
     </row>
-    <row r="162" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="24" t="s">
         <v>68</v>
       </c>
@@ -6368,8 +6368,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="164" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="164" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A164" s="131" t="s">
         <v>71</v>
       </c>
@@ -6379,7 +6379,7 @@
       <c r="E164" s="133"/>
       <c r="F164" s="134"/>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>1</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
         <v>6</v>
       </c>
@@ -6411,7 +6411,7 @@
       <c r="E166" s="3"/>
       <c r="F166" s="16"/>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="62" t="s">
         <v>72</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" s="7" t="s">
         <v>74</v>
       </c>
@@ -6444,7 +6444,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" s="7" t="s">
         <v>75</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" s="7" t="s">
         <v>76</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
         <v>77</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="7" t="s">
         <v>78</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
         <v>79</v>
       </c>
@@ -6528,7 +6528,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="7" t="s">
         <v>80</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
         <v>81</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" s="7" t="s">
         <v>82</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="7" t="s">
         <v>83</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" s="7" t="s">
         <v>84</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="7" t="s">
         <v>85</v>
       </c>
@@ -6650,7 +6650,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" s="7" t="s">
         <v>86</v>
       </c>
@@ -6672,7 +6672,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
         <v>87</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="7" t="s">
         <v>88</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="7" t="s">
         <v>89</v>
       </c>
@@ -6720,7 +6720,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" s="7" t="s">
         <v>78</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" s="7" t="s">
         <v>90</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="7" t="s">
         <v>91</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="7" t="s">
         <v>92</v>
       </c>
@@ -6808,7 +6808,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" s="7" t="s">
         <v>93</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="7" t="s">
         <v>94</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="7" t="s">
         <v>95</v>
       </c>
@@ -6874,7 +6874,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="7" t="s">
         <v>96</v>
       </c>
@@ -6896,7 +6896,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" s="7" t="s">
         <v>97</v>
       </c>
@@ -6910,7 +6910,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" s="7" t="s">
         <v>25</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="7" t="s">
         <v>98</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" s="7" t="s">
         <v>99</v>
       </c>
@@ -6966,7 +6966,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" s="7" t="s">
         <v>100</v>
       </c>
@@ -6988,7 +6988,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" s="7" t="s">
         <v>101</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="7" t="s">
         <v>102</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="7" t="s">
         <v>34</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="7" t="s">
         <v>103</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="7" t="s">
         <v>50</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="57" t="s">
         <v>11</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" s="11" t="s">
         <v>8</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" s="7" t="s">
         <v>104</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" s="7" t="s">
         <v>105</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" s="7" t="s">
         <v>106</v>
       </c>
@@ -7156,7 +7156,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" s="7" t="s">
         <v>101</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" s="7" t="s">
         <v>107</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" s="7" t="s">
         <v>108</v>
       </c>
@@ -7222,7 +7222,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" s="7" t="s">
         <v>109</v>
       </c>
@@ -7244,7 +7244,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" s="7" t="s">
         <v>110</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" s="7" t="s">
         <v>111</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" s="7" t="s">
         <v>103</v>
       </c>
@@ -7294,7 +7294,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" s="7" t="s">
         <v>50</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="57" t="s">
         <v>112</v>
       </c>
@@ -7322,7 +7322,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" s="11" t="s">
         <v>38</v>
       </c>
@@ -7332,7 +7332,7 @@
       <c r="E216" s="60"/>
       <c r="F216" s="14"/>
     </row>
-    <row r="217" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="17" t="s">
         <v>308</v>
       </c>
@@ -7354,8 +7354,8 @@
         <v>309</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="219" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="219" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A219" s="131" t="s">
         <v>226</v>
       </c>
@@ -7365,7 +7365,7 @@
       <c r="E219" s="133"/>
       <c r="F219" s="134"/>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>1</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" s="5" t="s">
         <v>6</v>
       </c>
@@ -7397,7 +7397,7 @@
       <c r="E221" s="3"/>
       <c r="F221" s="16"/>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" s="20" t="s">
         <v>113</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" s="20" t="s">
         <v>115</v>
       </c>
@@ -7441,7 +7441,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" s="20" t="s">
         <v>116</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" s="20" t="s">
         <v>117</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" s="20" t="s">
         <v>118</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="67" t="s">
         <v>119</v>
       </c>
@@ -7529,7 +7529,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" s="11" t="s">
         <v>8</v>
       </c>
@@ -7539,7 +7539,7 @@
       <c r="E228" s="60"/>
       <c r="F228" s="52"/>
     </row>
-    <row r="229" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="24" t="s">
         <v>65</v>
       </c>
@@ -7561,7 +7561,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" s="11" t="s">
         <v>38</v>
       </c>
@@ -7571,7 +7571,7 @@
       <c r="E230" s="60"/>
       <c r="F230" s="14"/>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" s="7" t="s">
         <v>120</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" s="7" t="s">
         <v>121</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="233" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="17" t="s">
         <v>122</v>
       </c>
@@ -7637,8 +7637,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="235" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="235" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A235" s="131" t="s">
         <v>227</v>
       </c>
@@ -7648,7 +7648,7 @@
       <c r="E235" s="133"/>
       <c r="F235" s="134"/>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>1</v>
       </c>
@@ -7668,7 +7668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" s="5" t="s">
         <v>6</v>
       </c>
@@ -7680,7 +7680,7 @@
       <c r="E237" s="2"/>
       <c r="F237" s="16"/>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238" s="83" t="s">
         <v>228</v>
       </c>
@@ -7690,7 +7690,7 @@
       <c r="E238" s="21"/>
       <c r="F238" s="56"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" s="83" t="s">
         <v>229</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" s="83" t="s">
         <v>230</v>
       </c>
@@ -7724,7 +7724,7 @@
       <c r="E240" s="21"/>
       <c r="F240" s="16"/>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" s="83" t="s">
         <v>231</v>
       </c>
@@ -7734,7 +7734,7 @@
       <c r="E241" s="21"/>
       <c r="F241" s="16"/>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" s="83" t="s">
         <v>232</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" s="83" t="s">
         <v>233</v>
       </c>
@@ -7778,7 +7778,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" s="38" t="s">
         <v>234</v>
       </c>
@@ -7800,7 +7800,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" s="83" t="s">
         <v>235</v>
       </c>
@@ -7822,7 +7822,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" s="38" t="s">
         <v>236</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" s="7" t="s">
         <v>230</v>
       </c>
@@ -7856,7 +7856,7 @@
       <c r="E247" s="21"/>
       <c r="F247" s="16"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" s="7" t="s">
         <v>76</v>
       </c>
@@ -7868,7 +7868,7 @@
       <c r="E248" s="21"/>
       <c r="F248" s="16"/>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" s="7" t="s">
         <v>237</v>
       </c>
@@ -7878,7 +7878,7 @@
       <c r="E249" s="21"/>
       <c r="F249" s="16"/>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" s="83" t="s">
         <v>238</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" s="83" t="s">
         <v>239</v>
       </c>
@@ -7922,7 +7922,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" s="83" t="s">
         <v>240</v>
       </c>
@@ -7944,7 +7944,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" s="83" t="s">
         <v>241</v>
       </c>
@@ -7966,7 +7966,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" s="83" t="s">
         <v>242</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" s="83" t="s">
         <v>243</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" s="83" t="s">
         <v>244</v>
       </c>
@@ -8032,7 +8032,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" s="83" t="s">
         <v>245</v>
       </c>
@@ -8054,7 +8054,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" s="83" t="s">
         <v>246</v>
       </c>
@@ -8076,7 +8076,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" s="83" t="s">
         <v>247</v>
       </c>
@@ -8098,7 +8098,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" s="83" t="s">
         <v>248</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" s="83" t="s">
         <v>249</v>
       </c>
@@ -8142,7 +8142,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" s="83" t="s">
         <v>250</v>
       </c>
@@ -8164,7 +8164,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" s="83" t="s">
         <v>76</v>
       </c>
@@ -8176,7 +8176,7 @@
       <c r="E263" s="21"/>
       <c r="F263" s="6"/>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" s="83" t="s">
         <v>25</v>
       </c>
@@ -8186,7 +8186,7 @@
       <c r="E264" s="21"/>
       <c r="F264" s="6"/>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" s="83" t="s">
         <v>251</v>
       </c>
@@ -8208,7 +8208,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" s="83" t="s">
         <v>252</v>
       </c>
@@ -8230,7 +8230,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" s="83" t="s">
         <v>253</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" s="83" t="s">
         <v>76</v>
       </c>
@@ -8264,7 +8264,7 @@
       <c r="E268" s="21"/>
       <c r="F268" s="6"/>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" s="83" t="s">
         <v>103</v>
       </c>
@@ -8276,7 +8276,7 @@
       <c r="E269" s="21"/>
       <c r="F269" s="6"/>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" s="83" t="s">
         <v>254</v>
       </c>
@@ -8286,7 +8286,7 @@
       <c r="E270" s="21"/>
       <c r="F270" s="6"/>
     </row>
-    <row r="271" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="85" t="s">
         <v>11</v>
       </c>
@@ -8296,7 +8296,7 @@
       <c r="E271" s="25"/>
       <c r="F271" s="10"/>
     </row>
-    <row r="272" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="96" t="s">
         <v>8</v>
       </c>
@@ -8306,7 +8306,7 @@
       <c r="E272" s="97"/>
       <c r="F272" s="98"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A273" s="99" t="s">
         <v>289</v>
       </c>
@@ -8316,7 +8316,7 @@
       <c r="E273" s="60"/>
       <c r="F273" s="14"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A274" s="83" t="s">
         <v>315</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A275" s="83" t="s">
         <v>291</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A276" s="83" t="s">
         <v>316</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" s="83" t="s">
         <v>317</v>
       </c>
@@ -8404,7 +8404,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A278" s="83" t="s">
         <v>314</v>
       </c>
@@ -8416,7 +8416,7 @@
       <c r="E278" s="21"/>
       <c r="F278" s="6"/>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A279" s="83" t="s">
         <v>105</v>
       </c>
@@ -8426,7 +8426,7 @@
       <c r="E279" s="21"/>
       <c r="F279" s="6"/>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A280" s="83" t="s">
         <v>318</v>
       </c>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="F280" s="6"/>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A281" s="83" t="s">
         <v>319</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A282" s="83" t="s">
         <v>320</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A283" s="83" t="s">
         <v>297</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A284" s="83" t="s">
         <v>299</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A285" s="83" t="s">
         <v>321</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A286" s="83" t="s">
         <v>322</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A287" s="83" t="s">
         <v>302</v>
       </c>
@@ -8590,7 +8590,7 @@
       <c r="E287" s="21"/>
       <c r="F287" s="6"/>
     </row>
-    <row r="288" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="85" t="s">
         <v>11</v>
       </c>
@@ -8602,7 +8602,7 @@
       <c r="E288" s="25"/>
       <c r="F288" s="10"/>
     </row>
-    <row r="289" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" ht="19" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A289" s="131" t="s">
         <v>337</v>
       </c>
@@ -8612,7 +8612,7 @@
       <c r="E289" s="133"/>
       <c r="F289" s="134"/>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A290" s="92" t="s">
         <v>1</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A291" s="5" t="s">
         <v>6</v>
       </c>
@@ -8644,7 +8644,7 @@
       <c r="E291" s="2"/>
       <c r="F291" s="16"/>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A292" s="86" t="s">
         <v>338</v>
       </c>
@@ -8654,7 +8654,7 @@
       <c r="E292" s="21"/>
       <c r="F292" s="6"/>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A293" s="83" t="s">
         <v>339</v>
       </c>
@@ -8676,7 +8676,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A294" s="83" t="s">
         <v>340</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A295" s="83" t="s">
         <v>341</v>
       </c>
@@ -8720,7 +8720,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A296" s="83" t="s">
         <v>342</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A297" s="83" t="s">
         <v>343</v>
       </c>
@@ -8764,7 +8764,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A298" s="83" t="s">
         <v>344</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A299" s="83" t="s">
         <v>345</v>
       </c>
@@ -8808,7 +8808,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A300" s="83" t="s">
         <v>346</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A301" s="83" t="s">
         <v>347</v>
       </c>
@@ -8852,7 +8852,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A302" s="86" t="s">
         <v>348</v>
       </c>
@@ -8862,7 +8862,7 @@
       <c r="E302" s="21"/>
       <c r="F302" s="6"/>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A303" s="83" t="s">
         <v>349</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A304" s="83" t="s">
         <v>350</v>
       </c>
@@ -8906,7 +8906,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A305" s="83" t="s">
         <v>351</v>
       </c>
@@ -8928,7 +8928,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="306" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="84" t="s">
         <v>352</v>
       </c>
@@ -8950,7 +8950,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A307" s="11" t="s">
         <v>8</v>
       </c>
@@ -8960,7 +8960,7 @@
       <c r="E307" s="60"/>
       <c r="F307" s="14"/>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A308" s="83" t="s">
         <v>65</v>
       </c>
@@ -8982,7 +8982,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A309" s="83" t="s">
         <v>358</v>
       </c>
@@ -9004,7 +9004,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A310" s="83" t="s">
         <v>359</v>
       </c>
@@ -9026,7 +9026,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="311" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A311" s="84" t="s">
         <v>360</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A312" s="11" t="s">
         <v>38</v>
       </c>
@@ -9058,7 +9058,7 @@
       <c r="E312" s="60"/>
       <c r="F312" s="14"/>
     </row>
-    <row r="313" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A313" s="106" t="s">
         <v>356</v>
       </c>
@@ -9080,12 +9080,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="314" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B314" s="81"/>
       <c r="C314" s="80"/>
       <c r="D314" s="101"/>
     </row>
-    <row r="315" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:6" ht="19" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A315" s="131" t="s">
         <v>365</v>
       </c>
@@ -9095,7 +9095,7 @@
       <c r="E315" s="133"/>
       <c r="F315" s="134"/>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A316" s="92" t="s">
         <v>1</v>
       </c>
@@ -9115,7 +9115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A317" s="5" t="s">
         <v>6</v>
       </c>
@@ -9127,7 +9127,7 @@
       <c r="E317" s="21"/>
       <c r="F317" s="6"/>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A318" s="20" t="s">
         <v>366</v>
       </c>
@@ -9137,7 +9137,7 @@
       <c r="E318" s="90"/>
       <c r="F318" s="16"/>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A319" s="20" t="s">
         <v>367</v>
       </c>
@@ -9157,7 +9157,7 @@
       </c>
       <c r="F319" s="16"/>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A320" s="20" t="s">
         <v>368</v>
       </c>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="F320" s="16"/>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A321" s="20" t="s">
         <v>369</v>
       </c>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="F321" s="16"/>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A322" s="20" t="s">
         <v>370</v>
       </c>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="F322" s="16"/>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A323" s="20" t="s">
         <v>371</v>
       </c>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="F323" s="16"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A324" s="20" t="s">
         <v>372</v>
       </c>
@@ -9249,7 +9249,7 @@
       <c r="E324" s="90"/>
       <c r="F324" s="16"/>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A325" s="20" t="s">
         <v>373</v>
       </c>
@@ -9259,7 +9259,7 @@
       <c r="E325" s="90"/>
       <c r="F325" s="16"/>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A326" s="20" t="s">
         <v>374</v>
       </c>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="F326" s="16"/>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A327" s="20" t="s">
         <v>375</v>
       </c>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="F327" s="16"/>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A328" s="20" t="s">
         <v>376</v>
       </c>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="F328" s="6"/>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A329" s="20" t="s">
         <v>377</v>
       </c>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="F329" s="16"/>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A330" s="20" t="s">
         <v>378</v>
       </c>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="F330" s="16"/>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A331" s="20" t="s">
         <v>379</v>
       </c>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="F331" s="6"/>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A332" s="20" t="s">
         <v>380</v>
       </c>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="F332" s="6"/>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A333" s="20" t="s">
         <v>381</v>
       </c>
@@ -9411,7 +9411,7 @@
       <c r="E333" s="90"/>
       <c r="F333" s="6"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A334" s="20" t="s">
         <v>382</v>
       </c>
@@ -9421,7 +9421,7 @@
       <c r="E334" s="90"/>
       <c r="F334" s="6"/>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A335" s="20" t="s">
         <v>269</v>
       </c>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F335" s="6"/>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A336" s="20" t="s">
         <v>383</v>
       </c>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="F336" s="6"/>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A337" s="20" t="s">
         <v>384</v>
       </c>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="F337" s="6"/>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A338" s="20" t="s">
         <v>385</v>
       </c>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="F338" s="6"/>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A339" s="20" t="s">
         <v>386</v>
       </c>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="F339" s="6"/>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A340" s="20" t="s">
         <v>271</v>
       </c>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="F340" s="6"/>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A341" s="20" t="s">
         <v>387</v>
       </c>
@@ -9553,7 +9553,7 @@
       <c r="E341" s="90"/>
       <c r="F341" s="6"/>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A342" s="20" t="s">
         <v>388</v>
       </c>
@@ -9563,7 +9563,7 @@
       <c r="E342" s="90"/>
       <c r="F342" s="6"/>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A343" s="20" t="s">
         <v>389</v>
       </c>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="F343" s="6"/>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A344" s="20" t="s">
         <v>390</v>
       </c>
@@ -9593,7 +9593,7 @@
       <c r="E344" s="90"/>
       <c r="F344" s="6"/>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A345" s="20" t="s">
         <v>278</v>
       </c>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="F345" s="6"/>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A346" s="20" t="s">
         <v>279</v>
       </c>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="F346" s="6"/>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A347" s="20" t="s">
         <v>391</v>
       </c>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="F347" s="6"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A348" s="20" t="s">
         <v>392</v>
       </c>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="F348" s="6"/>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A349" s="20" t="s">
         <v>281</v>
       </c>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="F349" s="6"/>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A350" s="20" t="s">
         <v>393</v>
       </c>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="F350" s="6"/>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A351" s="20" t="s">
         <v>394</v>
       </c>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="F351" s="6"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A352" s="20" t="s">
         <v>395</v>
       </c>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="F352" s="6"/>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A353" s="20" t="s">
         <v>396</v>
       </c>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="F353" s="6"/>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A354" s="20" t="s">
         <v>397</v>
       </c>
@@ -9785,7 +9785,7 @@
       <c r="E354" s="90"/>
       <c r="F354" s="6"/>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A355" s="20" t="s">
         <v>398</v>
       </c>
@@ -9795,7 +9795,7 @@
       <c r="E355" s="90"/>
       <c r="F355" s="6"/>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A356" s="20" t="s">
         <v>399</v>
       </c>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="F356" s="6"/>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A357" s="20" t="s">
         <v>400</v>
       </c>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="F357" s="6"/>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A358" s="20" t="s">
         <v>401</v>
       </c>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="F358" s="6"/>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A359" s="20" t="s">
         <v>402</v>
       </c>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="F359" s="6"/>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A360" s="20" t="s">
         <v>403</v>
       </c>
@@ -9887,7 +9887,7 @@
       <c r="E360" s="90"/>
       <c r="F360" s="6"/>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A361" s="20" t="s">
         <v>404</v>
       </c>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="F361" s="6"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A362" s="20" t="s">
         <v>405</v>
       </c>
@@ -9919,7 +9919,7 @@
       <c r="E362" s="90"/>
       <c r="F362" s="6"/>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A363" s="20" t="s">
         <v>285</v>
       </c>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="F363" s="6"/>
     </row>
-    <row r="364" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A364" s="67" t="s">
         <v>406</v>
       </c>
@@ -9951,7 +9951,7 @@
       <c r="E364" s="95"/>
       <c r="F364" s="72"/>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A365" s="11" t="s">
         <v>8</v>
       </c>
@@ -9961,7 +9961,7 @@
       <c r="E365" s="60"/>
       <c r="F365" s="14"/>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A366" s="20" t="s">
         <v>65</v>
       </c>
@@ -9971,7 +9971,7 @@
       <c r="E366" s="21"/>
       <c r="F366" s="6"/>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A367" s="20" t="s">
         <v>408</v>
       </c>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="F367" s="6"/>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A368" s="20" t="s">
         <v>409</v>
       </c>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="F368" s="6"/>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A369" s="20" t="s">
         <v>410</v>
       </c>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="F369" s="6"/>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A370" s="20" t="s">
         <v>271</v>
       </c>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="F370" s="6"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A371" s="20" t="s">
         <v>411</v>
       </c>
@@ -10063,7 +10063,7 @@
       <c r="E371" s="21"/>
       <c r="F371" s="6"/>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A372" s="20" t="s">
         <v>105</v>
       </c>
@@ -10073,7 +10073,7 @@
       <c r="E372" s="21"/>
       <c r="F372" s="6"/>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A373" s="20" t="s">
         <v>412</v>
       </c>
@@ -10093,7 +10093,7 @@
       </c>
       <c r="F373" s="6"/>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A374" s="20" t="s">
         <v>413</v>
       </c>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="F374" s="6"/>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A375" s="20" t="s">
         <v>414</v>
       </c>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="F375" s="6"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A376" s="20" t="s">
         <v>415</v>
       </c>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="F376" s="6"/>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A377" s="20" t="s">
         <v>416</v>
       </c>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="F377" s="6"/>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A378" s="20" t="s">
         <v>417</v>
       </c>
@@ -10185,7 +10185,7 @@
       <c r="E378" s="21"/>
       <c r="F378" s="6"/>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A379" s="20" t="s">
         <v>405</v>
       </c>
@@ -10197,7 +10197,7 @@
       <c r="E379" s="21"/>
       <c r="F379" s="6"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A380" s="20" t="s">
         <v>285</v>
       </c>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="F380" s="6"/>
     </row>
-    <row r="381" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A381" s="24" t="s">
         <v>418</v>
       </c>
@@ -10323,13 +10323,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A72D1499-D3A0-4266-A574-149D619EFB6A}">
   <dimension ref="A1:W24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="16" max="16" width="21.140625" customWidth="1"/>
+    <col min="16" max="16" width="21.1796875" customWidth="1"/>
     <col min="20" max="20" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="115" t="s">
         <v>0</v>
       </c>
@@ -10356,7 +10356,7 @@
       <c r="V1" s="116"/>
       <c r="W1" s="116"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="T3" s="120" t="s">
         <v>468</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="Q4" t="s">
         <v>466</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="P5" s="71" t="s">
         <v>451</v>
       </c>
@@ -10393,7 +10393,7 @@
         <v>0.39285714285714285</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="P6" s="71" t="s">
         <v>452</v>
       </c>
@@ -10412,7 +10412,7 @@
         <v>4.7619047619047616E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="P7" s="71" t="s">
         <v>453</v>
       </c>
@@ -10431,7 +10431,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="P8" t="s">
         <v>454</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>0.14285714285714285</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="P9" t="s">
         <v>455</v>
       </c>
@@ -10463,7 +10463,7 @@
         <v>0.13095238095238096</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="P10" t="s">
         <v>456</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>5.9523809523809521E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="P11" s="71" t="s">
         <v>457</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>4.7619047619047616E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="P12" s="71" t="s">
         <v>458</v>
       </c>
@@ -10517,7 +10517,7 @@
         <v>2.3809523809523808E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="P13" s="71" t="s">
         <v>459</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>2.3809523809523808E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="P14" s="71" t="s">
         <v>460</v>
       </c>
@@ -10555,7 +10555,7 @@
         <v>4.7619047619047616E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="P15" s="71" t="s">
         <v>461</v>
       </c>
@@ -10569,7 +10569,7 @@
       <c r="T15" s="123"/>
       <c r="U15" s="124"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="P16" t="s">
         <v>462</v>
       </c>
@@ -10580,7 +10580,7 @@
       <c r="T16" s="122"/>
       <c r="U16" s="125"/>
     </row>
-    <row r="17" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="16:21" x14ac:dyDescent="0.35">
       <c r="P17" s="71" t="s">
         <v>463</v>
       </c>
@@ -10594,7 +10594,7 @@
       <c r="T17" s="122"/>
       <c r="U17" s="125"/>
     </row>
-    <row r="18" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="16:21" x14ac:dyDescent="0.35">
       <c r="P18" t="s">
         <v>464</v>
       </c>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="R18" s="112"/>
     </row>
-    <row r="19" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="16:21" x14ac:dyDescent="0.35">
       <c r="P19" s="71" t="s">
         <v>465</v>
       </c>
@@ -10615,18 +10615,18 @@
         <v>0.39285714285714285</v>
       </c>
     </row>
-    <row r="20" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="16:21" x14ac:dyDescent="0.35">
       <c r="Q20" s="71">
         <f>SUM(Q5:Q7,Q11:Q15,Q17,Q19)</f>
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="16:21" x14ac:dyDescent="0.35">
       <c r="P22" s="71" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="23" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="16:21" x14ac:dyDescent="0.35">
       <c r="P23" t="s">
         <v>257</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>0.53533333333333433</v>
       </c>
     </row>
-    <row r="24" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="16:21" x14ac:dyDescent="0.35">
       <c r="P24" t="s">
         <v>258</v>
       </c>
@@ -10660,28 +10660,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9EEF34C-533F-4D76-B456-E79BEA524DCC}">
   <dimension ref="A1:AQ101"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.140625" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="1" max="1" width="26.1796875" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>2021</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>199</v>
       </c>
@@ -10868,7 +10868,7 @@
         <v>1213309.5172925084</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>470</v>
       </c>
@@ -10963,7 +10963,7 @@
         <v>546510.48924034019</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>205</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>2090069.7248419826</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>209</v>
       </c>
@@ -11153,12 +11153,12 @@
         <v>1406155.6987444595</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>2021</v>
       </c>
@@ -11250,7 +11250,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>199</v>
       </c>
@@ -11345,7 +11345,7 @@
         <v>2392614.7852066685</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>470</v>
       </c>
@@ -11440,7 +11440,7 @@
         <v>834725.65369765111</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>205</v>
       </c>
@@ -11535,7 +11535,7 @@
         <v>7911207.6996868448</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>209</v>
       </c>
@@ -11630,17 +11630,17 @@
         <v>2772902.4351726989</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>2021</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>199</v>
       </c>
@@ -11677,7 +11677,7 @@
       <c r="AD20" s="124"/>
       <c r="AE20" s="124"/>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>470</v>
       </c>
@@ -11714,7 +11714,7 @@
       <c r="AD21" s="124"/>
       <c r="AE21" s="124"/>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>205</v>
       </c>
@@ -11751,7 +11751,7 @@
       <c r="AD22" s="124"/>
       <c r="AE22" s="124"/>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>209</v>
       </c>
@@ -11788,17 +11788,17 @@
       <c r="AD23" s="124"/>
       <c r="AE23" s="124"/>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B26">
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>199</v>
       </c>
@@ -11806,7 +11806,7 @@
         <v>65750.800457615216</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>470</v>
       </c>
@@ -11814,7 +11814,7 @@
         <v>26096.967191940064</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>205</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>133213.1552570395</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>209</v>
       </c>
@@ -11830,17 +11830,17 @@
         <v>65750.800457615216</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B33">
         <v>2021</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>199</v>
       </c>
@@ -11877,7 +11877,7 @@
       <c r="AD34" s="124"/>
       <c r="AE34" s="124"/>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>470</v>
       </c>
@@ -11914,7 +11914,7 @@
       <c r="AD35" s="124"/>
       <c r="AE35" s="124"/>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>205</v>
       </c>
@@ -11951,7 +11951,7 @@
       <c r="AD36" s="124"/>
       <c r="AE36" s="124"/>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>209</v>
       </c>
@@ -11988,17 +11988,17 @@
       <c r="AD37" s="124"/>
       <c r="AE37" s="124"/>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B40">
         <v>2021</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>199</v>
       </c>
@@ -12007,7 +12007,7 @@
         <v>7.1681929364874337</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>470</v>
       </c>
@@ -12016,7 +12016,7 @@
         <v>1.6607160940325494</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>205</v>
       </c>
@@ -12025,7 +12025,7 @@
         <v>4.2704128132265557</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>209</v>
       </c>
@@ -12034,15 +12034,15 @@
         <v>12.14376215122577</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B45" s="124"/>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>487</v>
       </c>
@@ -12050,7 +12050,7 @@
         <v>91.94</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>488</v>
       </c>
@@ -12058,7 +12058,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>489</v>
       </c>
@@ -12066,12 +12066,12 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>491</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>492</v>
       </c>
@@ -12093,7 +12093,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>493</v>
       </c>
@@ -12104,7 +12104,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>494</v>
       </c>
@@ -12115,7 +12115,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>65</v>
       </c>
@@ -12126,12 +12126,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A59" s="126"/>
       <c r="B59" s="110" t="s">
         <v>163</v>
@@ -12260,7 +12260,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>199</v>
       </c>
@@ -12433,7 +12433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>470</v>
       </c>
@@ -12606,7 +12606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>205</v>
       </c>
@@ -12779,7 +12779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>209</v>
       </c>
@@ -12952,20 +12952,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:43" x14ac:dyDescent="0.35">
       <c r="B64" s="128"/>
     </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A67" s="126"/>
       <c r="B67" s="110" t="s">
         <v>163</v>
@@ -13094,7 +13094,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>199</v>
       </c>
@@ -13147,7 +13147,7 @@
       <c r="AP68" s="129"/>
       <c r="AQ68" s="129"/>
     </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>470</v>
       </c>
@@ -13200,7 +13200,7 @@
       <c r="AP69" s="129"/>
       <c r="AQ69" s="129"/>
     </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>205</v>
       </c>
@@ -13253,7 +13253,7 @@
       <c r="AP70" s="129"/>
       <c r="AQ70" s="129"/>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>209</v>
       </c>
@@ -13306,12 +13306,12 @@
       <c r="AP71" s="129"/>
       <c r="AQ71" s="129"/>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A74" s="126"/>
       <c r="B74" s="110" t="s">
         <v>163</v>
@@ -13440,7 +13440,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>199</v>
       </c>
@@ -13613,7 +13613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>470</v>
       </c>
@@ -13786,7 +13786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>205</v>
       </c>
@@ -13959,7 +13959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>209</v>
       </c>
@@ -14132,7 +14132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:43" x14ac:dyDescent="0.35">
       <c r="B79" s="128"/>
       <c r="C79" s="128"/>
       <c r="D79" s="128"/>
@@ -14176,17 +14176,17 @@
       <c r="AP79" s="128"/>
       <c r="AQ79" s="128"/>
     </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A82" s="126"/>
       <c r="B82" s="110" t="s">
         <v>163</v>
@@ -14315,7 +14315,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>199</v>
       </c>
@@ -14365,7 +14365,7 @@
       <c r="AP83" s="129"/>
       <c r="AQ83" s="129"/>
     </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>470</v>
       </c>
@@ -14415,7 +14415,7 @@
       <c r="AP84" s="129"/>
       <c r="AQ84" s="129"/>
     </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>205</v>
       </c>
@@ -14465,7 +14465,7 @@
       <c r="AP85" s="129"/>
       <c r="AQ85" s="129"/>
     </row>
-    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>209</v>
       </c>
@@ -14515,12 +14515,12 @@
       <c r="AP86" s="129"/>
       <c r="AQ86" s="129"/>
     </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A89" s="126"/>
       <c r="B89" s="110" t="s">
         <v>163</v>
@@ -14649,7 +14649,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>199</v>
       </c>
@@ -14822,7 +14822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>470</v>
       </c>
@@ -14995,7 +14995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>205</v>
       </c>
@@ -15168,7 +15168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>209</v>
       </c>
@@ -15341,20 +15341,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:43" x14ac:dyDescent="0.35">
       <c r="B94" s="128"/>
     </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A97" s="126"/>
       <c r="B97" s="110" t="s">
         <v>163</v>
@@ -15483,7 +15483,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>199</v>
       </c>
@@ -15533,7 +15533,7 @@
       <c r="AP98" s="129"/>
       <c r="AQ98" s="129"/>
     </row>
-    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>470</v>
       </c>
@@ -15583,7 +15583,7 @@
       <c r="AP99" s="129"/>
       <c r="AQ99" s="129"/>
     </row>
-    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>205</v>
       </c>
@@ -15633,7 +15633,7 @@
       <c r="AP100" s="129"/>
       <c r="AQ100" s="129"/>
     </row>
-    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>209</v>
       </c>
@@ -15694,33 +15694,33 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AS25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" customWidth="1"/>
-    <col min="14" max="24" width="7.7109375" customWidth="1"/>
-    <col min="25" max="26" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="9.7109375" customWidth="1"/>
-    <col min="29" max="33" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="43" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7265625" customWidth="1"/>
+    <col min="5" max="5" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7265625" customWidth="1"/>
+    <col min="14" max="24" width="7.7265625" customWidth="1"/>
+    <col min="25" max="26" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="9.7265625" customWidth="1"/>
+    <col min="29" max="33" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="41" max="43" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A1" s="126" t="s">
         <v>471</v>
       </c>
@@ -15851,7 +15851,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>199</v>
       </c>
@@ -16024,7 +16024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>469</v>
       </c>
@@ -16197,7 +16197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>470</v>
       </c>
@@ -16370,7 +16370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>200</v>
       </c>
@@ -16543,7 +16543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>201</v>
       </c>
@@ -16716,7 +16716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>202</v>
       </c>
@@ -16889,7 +16889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>203</v>
       </c>
@@ -17062,7 +17062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>204</v>
       </c>
@@ -17235,7 +17235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>205</v>
       </c>
@@ -17408,7 +17408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>206</v>
       </c>
@@ -17581,7 +17581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>207</v>
       </c>
@@ -17754,7 +17754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>208</v>
       </c>
@@ -17927,7 +17927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>209</v>
       </c>
@@ -18100,7 +18100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>210</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>211</v>
       </c>
@@ -18446,7 +18446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>212</v>
       </c>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>213</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>472</v>
       </c>
@@ -18966,7 +18966,7 @@
       </c>
       <c r="AS19" s="77"/>
     </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>473</v>
       </c>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="AS20" s="77"/>
     </row>
-    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>474</v>
       </c>
@@ -19314,7 +19314,7 @@
       </c>
       <c r="AS21" s="77"/>
     </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>475</v>
       </c>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="AS22" s="77"/>
     </row>
-    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>476</v>
       </c>
@@ -19661,7 +19661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A24" s="130" t="s">
         <v>511</v>
       </c>
@@ -19834,7 +19834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A25" s="130" t="s">
         <v>512</v>
       </c>
@@ -20019,32 +20019,32 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.453125" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7265625" customWidth="1"/>
+    <col min="5" max="5" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.1796875" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="13" max="24" width="8" customWidth="1"/>
-    <col min="25" max="26" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="9.7109375" customWidth="1"/>
-    <col min="29" max="33" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="7.140625" customWidth="1"/>
-    <col min="41" max="43" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="9.7265625" customWidth="1"/>
+    <col min="29" max="33" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="7.1796875" customWidth="1"/>
+    <col min="41" max="43" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A1" s="127" t="s">
         <v>471</v>
       </c>
@@ -20175,7 +20175,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>199</v>
       </c>
@@ -20348,7 +20348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>469</v>
       </c>
@@ -20521,7 +20521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>470</v>
       </c>
@@ -20694,7 +20694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>200</v>
       </c>
@@ -20867,7 +20867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>201</v>
       </c>
@@ -21040,7 +21040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>202</v>
       </c>
@@ -21213,7 +21213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>203</v>
       </c>
@@ -21386,7 +21386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>204</v>
       </c>
@@ -21559,7 +21559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>205</v>
       </c>
@@ -21732,7 +21732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>206</v>
       </c>
@@ -21905,7 +21905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>207</v>
       </c>
@@ -22078,7 +22078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>208</v>
       </c>
@@ -22251,7 +22251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>209</v>
       </c>
@@ -22424,7 +22424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>210</v>
       </c>
@@ -22597,7 +22597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>211</v>
       </c>
@@ -22770,7 +22770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>212</v>
       </c>
@@ -22943,7 +22943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>213</v>
       </c>
@@ -23116,7 +23116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>472</v>
       </c>
@@ -23289,7 +23289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>473</v>
       </c>
@@ -23462,7 +23462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>474</v>
       </c>
@@ -23635,7 +23635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>475</v>
       </c>
@@ -23808,7 +23808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>476</v>
       </c>
@@ -23981,7 +23981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A24" s="130" t="s">
         <v>511</v>
       </c>
@@ -24154,7 +24154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A25" s="130" t="s">
         <v>512</v>
       </c>
@@ -24338,32 +24338,32 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="24" width="8.28515625" customWidth="1"/>
-    <col min="25" max="26" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="9.7109375" customWidth="1"/>
-    <col min="29" max="33" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="43" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.453125" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7265625" customWidth="1"/>
+    <col min="5" max="5" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="24" width="8.26953125" customWidth="1"/>
+    <col min="25" max="26" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="9.7265625" customWidth="1"/>
+    <col min="29" max="33" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="41" max="43" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A1" s="127" t="s">
         <v>471</v>
       </c>
@@ -24494,7 +24494,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>199</v>
       </c>
@@ -24667,7 +24667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>469</v>
       </c>
@@ -24840,7 +24840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>470</v>
       </c>
@@ -25013,7 +25013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>200</v>
       </c>
@@ -25186,7 +25186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>201</v>
       </c>
@@ -25359,7 +25359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>202</v>
       </c>
@@ -25490,7 +25490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>203</v>
       </c>
@@ -25621,7 +25621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>204</v>
       </c>
@@ -25752,7 +25752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>205</v>
       </c>
@@ -25925,7 +25925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>206</v>
       </c>
@@ -26098,7 +26098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>207</v>
       </c>
@@ -26271,7 +26271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>208</v>
       </c>
@@ -26444,7 +26444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>209</v>
       </c>
@@ -26617,7 +26617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>210</v>
       </c>
@@ -26748,7 +26748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>211</v>
       </c>
@@ -26921,7 +26921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>212</v>
       </c>
@@ -27094,7 +27094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>213</v>
       </c>
@@ -27267,7 +27267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>472</v>
       </c>
@@ -27440,7 +27440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>473</v>
       </c>
@@ -27613,7 +27613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>474</v>
       </c>
@@ -27786,7 +27786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>475</v>
       </c>
@@ -27959,7 +27959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>476</v>
       </c>
@@ -28132,7 +28132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A24" s="130" t="s">
         <v>511</v>
       </c>
@@ -28305,7 +28305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A25" s="130" t="s">
         <v>512</v>
       </c>

--- a/InputData/elec/SoESCaOMCbIC/Share of Electricity Sector Capital and OM Costs by ISIC Code.xlsx
+++ b/InputData/elec/SoESCaOMCbIC/Share of Electricity Sector Capital and OM Costs by ISIC Code.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\elec\SoESCaOMCbIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\SoESCaOMCbIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9680A139-0A6F-4C1C-A62D-09CEA4056454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36B3B44-873D-4041-9BDC-E6592614157F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59445" yWindow="1200" windowWidth="24555" windowHeight="14835" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -2847,22 +2847,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="61.81640625" customWidth="1"/>
-    <col min="3" max="3" width="4.54296875" customWidth="1"/>
-    <col min="4" max="4" width="65.7265625" customWidth="1"/>
-    <col min="5" max="5" width="5.7265625" customWidth="1"/>
-    <col min="6" max="6" width="63.453125" customWidth="1"/>
-    <col min="8" max="8" width="52.81640625" customWidth="1"/>
+    <col min="2" max="2" width="61.85546875" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" customWidth="1"/>
+    <col min="4" max="4" width="65.7109375" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" customWidth="1"/>
+    <col min="6" max="6" width="63.42578125" customWidth="1"/>
+    <col min="8" max="8" width="52.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="71" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="71" t="s">
         <v>214</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>215</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" s="79">
         <v>2022</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>449</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="65" t="s">
         <v>448</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>450</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="78" t="s">
         <v>327</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>215</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="79">
         <v>2019</v>
       </c>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H12" s="79"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>287</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="65" t="s">
         <v>286</v>
       </c>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H14" s="65"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>288</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="78" t="s">
         <v>223</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>215</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="79">
         <v>2016</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B20" s="107" t="s">
         <v>224</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="109" t="s">
         <v>114</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>330</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="78" t="s">
         <v>328</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>215</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="79">
         <v>2016</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>329</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="65" t="s">
         <v>255</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>288</v>
       </c>
@@ -3159,37 +3159,37 @@
         <v>288</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="71" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>355</v>
       </c>
@@ -3215,19 +3215,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="77.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7265625" customWidth="1"/>
+    <col min="1" max="1" width="77.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="71" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="71" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="71" t="s">
         <v>194</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>429</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>430</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>447</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>125</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>126</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>127</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>128</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>129</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>428</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>427</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>130</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>440</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>441</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>442</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>443</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>131</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>132</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>133</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>134</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>135</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>136</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>137</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>444</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>445</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>446</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>138</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>139</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>140</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>141</v>
       </c>
@@ -3483,7 +3483,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>142</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>143</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>144</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>145</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>146</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>147</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>148</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>149</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>150</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>151</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>152</v>
       </c>
@@ -3579,17 +3579,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F381"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="65.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.1796875" customWidth="1"/>
-    <col min="4" max="4" width="23.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.54296875" customWidth="1"/>
-    <col min="6" max="6" width="60.453125" customWidth="1"/>
+    <col min="1" max="1" width="65.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.140625" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.5703125" customWidth="1"/>
+    <col min="6" max="6" width="60.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="135" t="s">
         <v>0</v>
       </c>
@@ -3599,7 +3599,7 @@
       <c r="E1" s="136"/>
       <c r="F1" s="137"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -3631,7 +3631,7 @@
       <c r="E3" s="21"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>153</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>154</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>155</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>156</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>157</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>158</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>159</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>160</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="57" t="s">
         <v>161</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" s="88" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>8</v>
       </c>
@@ -3871,7 +3871,7 @@
       <c r="E14" s="13"/>
       <c r="F14" s="14"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>257</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="87" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" s="87" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>258</v>
       </c>
@@ -3917,8 +3917,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="18" spans="1:6" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="131" t="s">
         <v>9</v>
       </c>
@@ -3928,7 +3928,7 @@
       <c r="E18" s="133"/>
       <c r="F18" s="134"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="92" t="s">
         <v>1</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>6</v>
       </c>
@@ -3960,7 +3960,7 @@
       <c r="E20" s="21"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>237</v>
       </c>
@@ -3970,7 +3970,7 @@
       <c r="E21" s="90"/>
       <c r="F21" s="56"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>259</v>
       </c>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="F22" s="16"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>260</v>
       </c>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="F23" s="16"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>261</v>
       </c>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="F24" s="16"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
         <v>262</v>
       </c>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="F25" s="16"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>263</v>
       </c>
@@ -4062,7 +4062,7 @@
       <c r="E26" s="90"/>
       <c r="F26" s="16"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
         <v>118</v>
       </c>
@@ -4072,7 +4072,7 @@
       <c r="E27" s="90"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
         <v>228</v>
       </c>
@@ -4082,7 +4082,7 @@
       <c r="E28" s="90"/>
       <c r="F28" s="16"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
         <v>264</v>
       </c>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="F29" s="16"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
         <v>265</v>
       </c>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F30" s="16"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
         <v>266</v>
       </c>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="F31" s="16"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
         <v>267</v>
       </c>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>268</v>
       </c>
@@ -4174,7 +4174,7 @@
       <c r="E33" s="90"/>
       <c r="F33" s="16"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
         <v>231</v>
       </c>
@@ -4184,7 +4184,7 @@
       <c r="E34" s="90"/>
       <c r="F34" s="16"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
         <v>269</v>
       </c>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="20" t="s">
         <v>270</v>
       </c>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
         <v>236</v>
       </c>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>271</v>
       </c>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
         <v>272</v>
       </c>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
         <v>273</v>
       </c>
@@ -4296,7 +4296,7 @@
       <c r="E40" s="21"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
         <v>274</v>
       </c>
@@ -4306,7 +4306,7 @@
       <c r="E41" s="21"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="20" t="s">
         <v>275</v>
       </c>
@@ -4316,7 +4316,7 @@
       <c r="E42" s="21"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
         <v>276</v>
       </c>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="20" t="s">
         <v>277</v>
       </c>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="20" t="s">
         <v>278</v>
       </c>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="20" t="s">
         <v>279</v>
       </c>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
         <v>280</v>
       </c>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="20" t="s">
         <v>281</v>
       </c>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
         <v>282</v>
       </c>
@@ -4448,7 +4448,7 @@
       <c r="E49" s="21"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="20" t="s">
         <v>283</v>
       </c>
@@ -4460,7 +4460,7 @@
       <c r="E50" s="21"/>
       <c r="F50" s="6"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="20" t="s">
         <v>284</v>
       </c>
@@ -4472,7 +4472,7 @@
       <c r="E51" s="21"/>
       <c r="F51" s="6"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="20" t="s">
         <v>285</v>
       </c>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="F52" s="6"/>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="24" t="s">
         <v>11</v>
       </c>
@@ -4504,7 +4504,7 @@
       <c r="E53" s="25"/>
       <c r="F53" s="10"/>
     </row>
-    <row r="54" spans="1:6" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" s="88" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>8</v>
       </c>
@@ -4514,7 +4514,7 @@
       <c r="E54" s="13"/>
       <c r="F54" s="14"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="20" t="s">
         <v>65</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="E55" s="21"/>
       <c r="F55" s="6"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="20" t="s">
         <v>289</v>
       </c>
@@ -4534,7 +4534,7 @@
       <c r="E56" s="21"/>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="20" t="s">
         <v>290</v>
       </c>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="20" t="s">
         <v>291</v>
       </c>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="F58" s="6"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="20" t="s">
         <v>292</v>
       </c>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="F59" s="6"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="20" t="s">
         <v>293</v>
       </c>
@@ -4606,7 +4606,7 @@
       <c r="E60" s="21"/>
       <c r="F60" s="6"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
         <v>105</v>
       </c>
@@ -4616,7 +4616,7 @@
       <c r="E61" s="21"/>
       <c r="F61" s="6"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="20" t="s">
         <v>294</v>
       </c>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="F62" s="6"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="20" t="s">
         <v>295</v>
       </c>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
         <v>296</v>
       </c>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="20" t="s">
         <v>297</v>
       </c>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="20" t="s">
         <v>298</v>
       </c>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="20" t="s">
         <v>299</v>
       </c>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="20" t="s">
         <v>300</v>
       </c>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="20" t="s">
         <v>301</v>
       </c>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="20" t="s">
         <v>302</v>
       </c>
@@ -4788,7 +4788,7 @@
       <c r="E70" s="21"/>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="20" t="s">
         <v>50</v>
       </c>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="F71" s="6"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="20" t="s">
         <v>303</v>
       </c>
@@ -4820,7 +4820,7 @@
       <c r="E72" s="21"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="24" t="s">
         <v>304</v>
       </c>
@@ -4832,8 +4832,8 @@
       <c r="E73" s="25"/>
       <c r="F73" s="10"/>
     </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="75" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A75" s="135" t="s">
         <v>12</v>
       </c>
@@ -4843,7 +4843,7 @@
       <c r="E75" s="138"/>
       <c r="F75" s="137"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>1</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
         <v>6</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>14</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>16</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
         <v>17</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
         <v>18</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="30" t="s">
         <v>19</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>20</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>21</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>22</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="30" t="s">
         <v>23</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="30" t="s">
         <v>24</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>25</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
         <v>26</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
         <v>27</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>28</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>29</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>30</v>
       </c>
@@ -5171,7 +5171,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>31</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>32</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
         <v>33</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="30" t="s">
         <v>34</v>
       </c>
@@ -5250,7 +5250,7 @@
       <c r="E97" s="73"/>
       <c r="F97" s="16"/>
     </row>
-    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="31" t="s">
         <v>35</v>
       </c>
@@ -5263,7 +5263,7 @@
       <c r="E98" s="34"/>
       <c r="F98" s="35"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
         <v>8</v>
       </c>
@@ -5273,7 +5273,7 @@
       <c r="E99" s="37"/>
       <c r="F99" s="14"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="38" t="s">
         <v>20</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="38" t="s">
         <v>36</v>
       </c>
@@ -5317,7 +5317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="38" t="s">
         <v>37</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="40" t="s">
         <v>35</v>
       </c>
@@ -5352,7 +5352,7 @@
       <c r="E103" s="43"/>
       <c r="F103" s="10"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
         <v>38</v>
       </c>
@@ -5362,7 +5362,7 @@
       <c r="E104" s="37"/>
       <c r="F104" s="14"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="38" t="s">
         <v>39</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="38" t="s">
         <v>40</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="38" t="s">
         <v>29</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="40" t="s">
         <v>35</v>
       </c>
@@ -5441,8 +5441,8 @@
       <c r="E108" s="43"/>
       <c r="F108" s="10"/>
     </row>
-    <row r="109" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="110" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A110" s="135" t="s">
         <v>41</v>
       </c>
@@ -5452,7 +5452,7 @@
       <c r="E110" s="138"/>
       <c r="F110" s="137"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>1</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
         <v>6</v>
       </c>
@@ -5484,12 +5484,12 @@
       <c r="E112" s="3"/>
       <c r="F112" s="16"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>16</v>
       </c>
@@ -5511,7 +5511,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
         <v>17</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
         <v>18</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
         <v>43</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
         <v>44</v>
       </c>
@@ -5581,7 +5581,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>21</v>
       </c>
@@ -5603,7 +5603,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
         <v>45</v>
       </c>
@@ -5625,7 +5625,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
         <v>46</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
         <v>43</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
         <v>24</v>
       </c>
@@ -5675,7 +5675,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
         <v>25</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
         <v>47</v>
       </c>
@@ -5709,7 +5709,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
         <v>27</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
         <v>28</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
         <v>48</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
         <v>30</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
         <v>33</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
         <v>34</v>
       </c>
@@ -5831,7 +5831,7 @@
       <c r="E131" s="73"/>
       <c r="F131" s="16"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
         <v>49</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="47" t="s">
         <v>50</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
         <v>8</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="38" t="s">
         <v>20</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="38" t="s">
         <v>36</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="38" t="s">
         <v>37</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="40" t="s">
         <v>35</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
         <v>38</v>
       </c>
@@ -5963,7 +5963,7 @@
       <c r="E139" s="37"/>
       <c r="F139" s="14"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="38" t="s">
         <v>51</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="38" t="s">
         <v>40</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="38" t="s">
         <v>29</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="40" t="s">
         <v>35</v>
       </c>
@@ -6042,8 +6042,8 @@
       <c r="E143" s="26"/>
       <c r="F143" s="10"/>
     </row>
-    <row r="144" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="145" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="145" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A145" s="131" t="s">
         <v>52</v>
       </c>
@@ -6053,7 +6053,7 @@
       <c r="E145" s="133"/>
       <c r="F145" s="134"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>1</v>
       </c>
@@ -6073,7 +6073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
         <v>6</v>
       </c>
@@ -6085,7 +6085,7 @@
       <c r="E147" s="3"/>
       <c r="F147" s="16"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
         <v>53</v>
       </c>
@@ -6095,7 +6095,7 @@
       <c r="E148" s="22"/>
       <c r="F148" s="6"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
         <v>54</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
         <v>57</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
         <v>58</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
         <v>59</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
         <v>60</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
         <v>61</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
         <v>62</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
         <v>63</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
         <v>64</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="57" t="s">
         <v>11</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>8</v>
       </c>
@@ -6314,7 +6314,7 @@
       <c r="E159" s="60"/>
       <c r="F159" s="14"/>
     </row>
-    <row r="160" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="57" t="s">
         <v>65</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
         <v>38</v>
       </c>
@@ -6346,7 +6346,7 @@
       <c r="E161" s="60"/>
       <c r="F161" s="14"/>
     </row>
-    <row r="162" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="24" t="s">
         <v>68</v>
       </c>
@@ -6368,8 +6368,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="164" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="164" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A164" s="131" t="s">
         <v>71</v>
       </c>
@@ -6379,7 +6379,7 @@
       <c r="E164" s="133"/>
       <c r="F164" s="134"/>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>1</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
         <v>6</v>
       </c>
@@ -6411,7 +6411,7 @@
       <c r="E166" s="3"/>
       <c r="F166" s="16"/>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="62" t="s">
         <v>72</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
         <v>74</v>
       </c>
@@ -6444,7 +6444,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
         <v>75</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
         <v>76</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
         <v>77</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
         <v>78</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
         <v>79</v>
       </c>
@@ -6528,7 +6528,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
         <v>80</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
         <v>81</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>82</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
         <v>83</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
         <v>84</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
         <v>85</v>
       </c>
@@ -6650,7 +6650,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
         <v>86</v>
       </c>
@@ -6672,7 +6672,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>87</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
         <v>88</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
         <v>89</v>
       </c>
@@ -6720,7 +6720,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
         <v>78</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
         <v>90</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
         <v>91</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
         <v>92</v>
       </c>
@@ -6808,7 +6808,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
         <v>93</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
         <v>94</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
         <v>95</v>
       </c>
@@ -6874,7 +6874,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
         <v>96</v>
       </c>
@@ -6896,7 +6896,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
         <v>97</v>
       </c>
@@ -6910,7 +6910,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
         <v>25</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
         <v>98</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
         <v>99</v>
       </c>
@@ -6966,7 +6966,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
         <v>100</v>
       </c>
@@ -6988,7 +6988,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>101</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>102</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>34</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>103</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>50</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="57" t="s">
         <v>11</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="11" t="s">
         <v>8</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
         <v>104</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
         <v>105</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
         <v>106</v>
       </c>
@@ -7156,7 +7156,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
         <v>101</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
         <v>107</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
         <v>108</v>
       </c>
@@ -7222,7 +7222,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="7" t="s">
         <v>109</v>
       </c>
@@ -7244,7 +7244,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
         <v>110</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
         <v>111</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
         <v>103</v>
       </c>
@@ -7294,7 +7294,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="7" t="s">
         <v>50</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="57" t="s">
         <v>112</v>
       </c>
@@ -7322,7 +7322,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
         <v>38</v>
       </c>
@@ -7332,7 +7332,7 @@
       <c r="E216" s="60"/>
       <c r="F216" s="14"/>
     </row>
-    <row r="217" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="17" t="s">
         <v>308</v>
       </c>
@@ -7354,8 +7354,8 @@
         <v>309</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="219" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="219" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A219" s="131" t="s">
         <v>226</v>
       </c>
@@ -7365,7 +7365,7 @@
       <c r="E219" s="133"/>
       <c r="F219" s="134"/>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>1</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
         <v>6</v>
       </c>
@@ -7397,7 +7397,7 @@
       <c r="E221" s="3"/>
       <c r="F221" s="16"/>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="20" t="s">
         <v>113</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="20" t="s">
         <v>115</v>
       </c>
@@ -7441,7 +7441,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="20" t="s">
         <v>116</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="20" t="s">
         <v>117</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="20" t="s">
         <v>118</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="67" t="s">
         <v>119</v>
       </c>
@@ -7529,7 +7529,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
         <v>8</v>
       </c>
@@ -7539,7 +7539,7 @@
       <c r="E228" s="60"/>
       <c r="F228" s="52"/>
     </row>
-    <row r="229" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="24" t="s">
         <v>65</v>
       </c>
@@ -7561,7 +7561,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
         <v>38</v>
       </c>
@@ -7571,7 +7571,7 @@
       <c r="E230" s="60"/>
       <c r="F230" s="14"/>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
         <v>120</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
         <v>121</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="233" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="17" t="s">
         <v>122</v>
       </c>
@@ -7637,8 +7637,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="235" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="235" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A235" s="131" t="s">
         <v>227</v>
       </c>
@@ -7648,7 +7648,7 @@
       <c r="E235" s="133"/>
       <c r="F235" s="134"/>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>1</v>
       </c>
@@ -7668,7 +7668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="s">
         <v>6</v>
       </c>
@@ -7680,7 +7680,7 @@
       <c r="E237" s="2"/>
       <c r="F237" s="16"/>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="83" t="s">
         <v>228</v>
       </c>
@@ -7690,7 +7690,7 @@
       <c r="E238" s="21"/>
       <c r="F238" s="56"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="83" t="s">
         <v>229</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="83" t="s">
         <v>230</v>
       </c>
@@ -7724,7 +7724,7 @@
       <c r="E240" s="21"/>
       <c r="F240" s="16"/>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="83" t="s">
         <v>231</v>
       </c>
@@ -7734,7 +7734,7 @@
       <c r="E241" s="21"/>
       <c r="F241" s="16"/>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="83" t="s">
         <v>232</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="83" t="s">
         <v>233</v>
       </c>
@@ -7778,7 +7778,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="38" t="s">
         <v>234</v>
       </c>
@@ -7800,7 +7800,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="83" t="s">
         <v>235</v>
       </c>
@@ -7822,7 +7822,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="38" t="s">
         <v>236</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
         <v>230</v>
       </c>
@@ -7856,7 +7856,7 @@
       <c r="E247" s="21"/>
       <c r="F247" s="16"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="7" t="s">
         <v>76</v>
       </c>
@@ -7868,7 +7868,7 @@
       <c r="E248" s="21"/>
       <c r="F248" s="16"/>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
         <v>237</v>
       </c>
@@ -7878,7 +7878,7 @@
       <c r="E249" s="21"/>
       <c r="F249" s="16"/>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="83" t="s">
         <v>238</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="83" t="s">
         <v>239</v>
       </c>
@@ -7922,7 +7922,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="83" t="s">
         <v>240</v>
       </c>
@@ -7944,7 +7944,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="83" t="s">
         <v>241</v>
       </c>
@@ -7966,7 +7966,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="83" t="s">
         <v>242</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="83" t="s">
         <v>243</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="83" t="s">
         <v>244</v>
       </c>
@@ -8032,7 +8032,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="83" t="s">
         <v>245</v>
       </c>
@@ -8054,7 +8054,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="83" t="s">
         <v>246</v>
       </c>
@@ -8076,7 +8076,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="83" t="s">
         <v>247</v>
       </c>
@@ -8098,7 +8098,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="83" t="s">
         <v>248</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="83" t="s">
         <v>249</v>
       </c>
@@ -8142,7 +8142,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="83" t="s">
         <v>250</v>
       </c>
@@ -8164,7 +8164,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="83" t="s">
         <v>76</v>
       </c>
@@ -8176,7 +8176,7 @@
       <c r="E263" s="21"/>
       <c r="F263" s="6"/>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="83" t="s">
         <v>25</v>
       </c>
@@ -8186,7 +8186,7 @@
       <c r="E264" s="21"/>
       <c r="F264" s="6"/>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="83" t="s">
         <v>251</v>
       </c>
@@ -8208,7 +8208,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="83" t="s">
         <v>252</v>
       </c>
@@ -8230,7 +8230,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="83" t="s">
         <v>253</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="83" t="s">
         <v>76</v>
       </c>
@@ -8264,7 +8264,7 @@
       <c r="E268" s="21"/>
       <c r="F268" s="6"/>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="83" t="s">
         <v>103</v>
       </c>
@@ -8276,7 +8276,7 @@
       <c r="E269" s="21"/>
       <c r="F269" s="6"/>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="83" t="s">
         <v>254</v>
       </c>
@@ -8286,7 +8286,7 @@
       <c r="E270" s="21"/>
       <c r="F270" s="6"/>
     </row>
-    <row r="271" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="85" t="s">
         <v>11</v>
       </c>
@@ -8296,7 +8296,7 @@
       <c r="E271" s="25"/>
       <c r="F271" s="10"/>
     </row>
-    <row r="272" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="96" t="s">
         <v>8</v>
       </c>
@@ -8306,7 +8306,7 @@
       <c r="E272" s="97"/>
       <c r="F272" s="98"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="99" t="s">
         <v>289</v>
       </c>
@@ -8316,7 +8316,7 @@
       <c r="E273" s="60"/>
       <c r="F273" s="14"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="83" t="s">
         <v>315</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="83" t="s">
         <v>291</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="83" t="s">
         <v>316</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="83" t="s">
         <v>317</v>
       </c>
@@ -8404,7 +8404,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="83" t="s">
         <v>314</v>
       </c>
@@ -8416,7 +8416,7 @@
       <c r="E278" s="21"/>
       <c r="F278" s="6"/>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="83" t="s">
         <v>105</v>
       </c>
@@ -8426,7 +8426,7 @@
       <c r="E279" s="21"/>
       <c r="F279" s="6"/>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="83" t="s">
         <v>318</v>
       </c>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="F280" s="6"/>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="83" t="s">
         <v>319</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="83" t="s">
         <v>320</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="83" t="s">
         <v>297</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="83" t="s">
         <v>299</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="83" t="s">
         <v>321</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="83" t="s">
         <v>322</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="83" t="s">
         <v>302</v>
       </c>
@@ -8590,7 +8590,7 @@
       <c r="E287" s="21"/>
       <c r="F287" s="6"/>
     </row>
-    <row r="288" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="85" t="s">
         <v>11</v>
       </c>
@@ -8602,7 +8602,7 @@
       <c r="E288" s="25"/>
       <c r="F288" s="10"/>
     </row>
-    <row r="289" spans="1:6" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="289" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A289" s="131" t="s">
         <v>337</v>
       </c>
@@ -8612,7 +8612,7 @@
       <c r="E289" s="133"/>
       <c r="F289" s="134"/>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="92" t="s">
         <v>1</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="5" t="s">
         <v>6</v>
       </c>
@@ -8644,7 +8644,7 @@
       <c r="E291" s="2"/>
       <c r="F291" s="16"/>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="86" t="s">
         <v>338</v>
       </c>
@@ -8654,7 +8654,7 @@
       <c r="E292" s="21"/>
       <c r="F292" s="6"/>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="83" t="s">
         <v>339</v>
       </c>
@@ -8676,7 +8676,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="83" t="s">
         <v>340</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="83" t="s">
         <v>341</v>
       </c>
@@ -8720,7 +8720,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="83" t="s">
         <v>342</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="83" t="s">
         <v>343</v>
       </c>
@@ -8764,7 +8764,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="83" t="s">
         <v>344</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="83" t="s">
         <v>345</v>
       </c>
@@ -8808,7 +8808,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="83" t="s">
         <v>346</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="83" t="s">
         <v>347</v>
       </c>
@@ -8852,7 +8852,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="86" t="s">
         <v>348</v>
       </c>
@@ -8862,7 +8862,7 @@
       <c r="E302" s="21"/>
       <c r="F302" s="6"/>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="83" t="s">
         <v>349</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="83" t="s">
         <v>350</v>
       </c>
@@ -8906,7 +8906,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="83" t="s">
         <v>351</v>
       </c>
@@ -8928,7 +8928,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="306" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="84" t="s">
         <v>352</v>
       </c>
@@ -8950,7 +8950,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="11" t="s">
         <v>8</v>
       </c>
@@ -8960,7 +8960,7 @@
       <c r="E307" s="60"/>
       <c r="F307" s="14"/>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="83" t="s">
         <v>65</v>
       </c>
@@ -8982,7 +8982,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="83" t="s">
         <v>358</v>
       </c>
@@ -9004,7 +9004,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="83" t="s">
         <v>359</v>
       </c>
@@ -9026,7 +9026,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="311" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="84" t="s">
         <v>360</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="11" t="s">
         <v>38</v>
       </c>
@@ -9058,7 +9058,7 @@
       <c r="E312" s="60"/>
       <c r="F312" s="14"/>
     </row>
-    <row r="313" spans="1:6" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="106" t="s">
         <v>356</v>
       </c>
@@ -9080,12 +9080,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="314" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B314" s="81"/>
       <c r="C314" s="80"/>
       <c r="D314" s="101"/>
     </row>
-    <row r="315" spans="1:6" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="315" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A315" s="131" t="s">
         <v>365</v>
       </c>
@@ -9095,7 +9095,7 @@
       <c r="E315" s="133"/>
       <c r="F315" s="134"/>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="92" t="s">
         <v>1</v>
       </c>
@@ -9115,7 +9115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="5" t="s">
         <v>6</v>
       </c>
@@ -9127,7 +9127,7 @@
       <c r="E317" s="21"/>
       <c r="F317" s="6"/>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="20" t="s">
         <v>366</v>
       </c>
@@ -9137,7 +9137,7 @@
       <c r="E318" s="90"/>
       <c r="F318" s="16"/>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="20" t="s">
         <v>367</v>
       </c>
@@ -9157,7 +9157,7 @@
       </c>
       <c r="F319" s="16"/>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="20" t="s">
         <v>368</v>
       </c>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="F320" s="16"/>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="20" t="s">
         <v>369</v>
       </c>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="F321" s="16"/>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="20" t="s">
         <v>370</v>
       </c>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="F322" s="16"/>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="20" t="s">
         <v>371</v>
       </c>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="F323" s="16"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="20" t="s">
         <v>372</v>
       </c>
@@ -9249,7 +9249,7 @@
       <c r="E324" s="90"/>
       <c r="F324" s="16"/>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="20" t="s">
         <v>373</v>
       </c>
@@ -9259,7 +9259,7 @@
       <c r="E325" s="90"/>
       <c r="F325" s="16"/>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="20" t="s">
         <v>374</v>
       </c>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="F326" s="16"/>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="20" t="s">
         <v>375</v>
       </c>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="F327" s="16"/>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="20" t="s">
         <v>376</v>
       </c>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="F328" s="6"/>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="20" t="s">
         <v>377</v>
       </c>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="F329" s="16"/>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="20" t="s">
         <v>378</v>
       </c>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="F330" s="16"/>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="20" t="s">
         <v>379</v>
       </c>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="F331" s="6"/>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="20" t="s">
         <v>380</v>
       </c>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="F332" s="6"/>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="20" t="s">
         <v>381</v>
       </c>
@@ -9411,7 +9411,7 @@
       <c r="E333" s="90"/>
       <c r="F333" s="6"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="20" t="s">
         <v>382</v>
       </c>
@@ -9421,7 +9421,7 @@
       <c r="E334" s="90"/>
       <c r="F334" s="6"/>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="20" t="s">
         <v>269</v>
       </c>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F335" s="6"/>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="20" t="s">
         <v>383</v>
       </c>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="F336" s="6"/>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="20" t="s">
         <v>384</v>
       </c>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="F337" s="6"/>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="20" t="s">
         <v>385</v>
       </c>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="F338" s="6"/>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="20" t="s">
         <v>386</v>
       </c>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="F339" s="6"/>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="20" t="s">
         <v>271</v>
       </c>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="F340" s="6"/>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="20" t="s">
         <v>387</v>
       </c>
@@ -9553,7 +9553,7 @@
       <c r="E341" s="90"/>
       <c r="F341" s="6"/>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="20" t="s">
         <v>388</v>
       </c>
@@ -9563,7 +9563,7 @@
       <c r="E342" s="90"/>
       <c r="F342" s="6"/>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="20" t="s">
         <v>389</v>
       </c>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="F343" s="6"/>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="20" t="s">
         <v>390</v>
       </c>
@@ -9593,7 +9593,7 @@
       <c r="E344" s="90"/>
       <c r="F344" s="6"/>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="20" t="s">
         <v>278</v>
       </c>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="F345" s="6"/>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="20" t="s">
         <v>279</v>
       </c>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="F346" s="6"/>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="20" t="s">
         <v>391</v>
       </c>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="F347" s="6"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="20" t="s">
         <v>392</v>
       </c>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="F348" s="6"/>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="20" t="s">
         <v>281</v>
       </c>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="F349" s="6"/>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="20" t="s">
         <v>393</v>
       </c>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="F350" s="6"/>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="20" t="s">
         <v>394</v>
       </c>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="F351" s="6"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="20" t="s">
         <v>395</v>
       </c>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="F352" s="6"/>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="20" t="s">
         <v>396</v>
       </c>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="F353" s="6"/>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="20" t="s">
         <v>397</v>
       </c>
@@ -9785,7 +9785,7 @@
       <c r="E354" s="90"/>
       <c r="F354" s="6"/>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="20" t="s">
         <v>398</v>
       </c>
@@ -9795,7 +9795,7 @@
       <c r="E355" s="90"/>
       <c r="F355" s="6"/>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="20" t="s">
         <v>399</v>
       </c>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="F356" s="6"/>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="20" t="s">
         <v>400</v>
       </c>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="F357" s="6"/>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="20" t="s">
         <v>401</v>
       </c>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="F358" s="6"/>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="20" t="s">
         <v>402</v>
       </c>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="F359" s="6"/>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="20" t="s">
         <v>403</v>
       </c>
@@ -9887,7 +9887,7 @@
       <c r="E360" s="90"/>
       <c r="F360" s="6"/>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="20" t="s">
         <v>404</v>
       </c>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="F361" s="6"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="20" t="s">
         <v>405</v>
       </c>
@@ -9919,7 +9919,7 @@
       <c r="E362" s="90"/>
       <c r="F362" s="6"/>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="20" t="s">
         <v>285</v>
       </c>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="F363" s="6"/>
     </row>
-    <row r="364" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="67" t="s">
         <v>406</v>
       </c>
@@ -9951,7 +9951,7 @@
       <c r="E364" s="95"/>
       <c r="F364" s="72"/>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="11" t="s">
         <v>8</v>
       </c>
@@ -9961,7 +9961,7 @@
       <c r="E365" s="60"/>
       <c r="F365" s="14"/>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="20" t="s">
         <v>65</v>
       </c>
@@ -9971,7 +9971,7 @@
       <c r="E366" s="21"/>
       <c r="F366" s="6"/>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="20" t="s">
         <v>408</v>
       </c>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="F367" s="6"/>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="20" t="s">
         <v>409</v>
       </c>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="F368" s="6"/>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="20" t="s">
         <v>410</v>
       </c>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="F369" s="6"/>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="20" t="s">
         <v>271</v>
       </c>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="F370" s="6"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="20" t="s">
         <v>411</v>
       </c>
@@ -10063,7 +10063,7 @@
       <c r="E371" s="21"/>
       <c r="F371" s="6"/>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="20" t="s">
         <v>105</v>
       </c>
@@ -10073,7 +10073,7 @@
       <c r="E372" s="21"/>
       <c r="F372" s="6"/>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="20" t="s">
         <v>412</v>
       </c>
@@ -10093,7 +10093,7 @@
       </c>
       <c r="F373" s="6"/>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="20" t="s">
         <v>413</v>
       </c>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="F374" s="6"/>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="20" t="s">
         <v>414</v>
       </c>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="F375" s="6"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="20" t="s">
         <v>415</v>
       </c>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="F376" s="6"/>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="20" t="s">
         <v>416</v>
       </c>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="F377" s="6"/>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="20" t="s">
         <v>417</v>
       </c>
@@ -10185,7 +10185,7 @@
       <c r="E378" s="21"/>
       <c r="F378" s="6"/>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="20" t="s">
         <v>405</v>
       </c>
@@ -10197,7 +10197,7 @@
       <c r="E379" s="21"/>
       <c r="F379" s="6"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="20" t="s">
         <v>285</v>
       </c>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="F380" s="6"/>
     </row>
-    <row r="381" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="24" t="s">
         <v>418</v>
       </c>
@@ -10323,13 +10323,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A72D1499-D3A0-4266-A574-149D619EFB6A}">
   <dimension ref="A1:W24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="16" max="16" width="21.1796875" customWidth="1"/>
+    <col min="16" max="16" width="21.140625" customWidth="1"/>
     <col min="20" max="20" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="115" t="s">
         <v>0</v>
       </c>
@@ -10356,7 +10356,7 @@
       <c r="V1" s="116"/>
       <c r="W1" s="116"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="T3" s="120" t="s">
         <v>468</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="Q4" t="s">
         <v>466</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="P5" s="71" t="s">
         <v>451</v>
       </c>
@@ -10393,7 +10393,7 @@
         <v>0.39285714285714285</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="P6" s="71" t="s">
         <v>452</v>
       </c>
@@ -10412,7 +10412,7 @@
         <v>4.7619047619047616E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="P7" s="71" t="s">
         <v>453</v>
       </c>
@@ -10431,7 +10431,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="P8" t="s">
         <v>454</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>0.14285714285714285</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="P9" t="s">
         <v>455</v>
       </c>
@@ -10463,7 +10463,7 @@
         <v>0.13095238095238096</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="P10" t="s">
         <v>456</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>5.9523809523809521E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="P11" s="71" t="s">
         <v>457</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>4.7619047619047616E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="P12" s="71" t="s">
         <v>458</v>
       </c>
@@ -10517,7 +10517,7 @@
         <v>2.3809523809523808E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="P13" s="71" t="s">
         <v>459</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>2.3809523809523808E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="P14" s="71" t="s">
         <v>460</v>
       </c>
@@ -10555,7 +10555,7 @@
         <v>4.7619047619047616E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="P15" s="71" t="s">
         <v>461</v>
       </c>
@@ -10569,7 +10569,7 @@
       <c r="T15" s="123"/>
       <c r="U15" s="124"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="P16" t="s">
         <v>462</v>
       </c>
@@ -10580,7 +10580,7 @@
       <c r="T16" s="122"/>
       <c r="U16" s="125"/>
     </row>
-    <row r="17" spans="16:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="16:21" x14ac:dyDescent="0.25">
       <c r="P17" s="71" t="s">
         <v>463</v>
       </c>
@@ -10594,7 +10594,7 @@
       <c r="T17" s="122"/>
       <c r="U17" s="125"/>
     </row>
-    <row r="18" spans="16:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="16:21" x14ac:dyDescent="0.25">
       <c r="P18" t="s">
         <v>464</v>
       </c>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="R18" s="112"/>
     </row>
-    <row r="19" spans="16:21" x14ac:dyDescent="0.35">
+    <row r="19" spans="16:21" x14ac:dyDescent="0.25">
       <c r="P19" s="71" t="s">
         <v>465</v>
       </c>
@@ -10615,18 +10615,18 @@
         <v>0.39285714285714285</v>
       </c>
     </row>
-    <row r="20" spans="16:21" x14ac:dyDescent="0.35">
+    <row r="20" spans="16:21" x14ac:dyDescent="0.25">
       <c r="Q20" s="71">
         <f>SUM(Q5:Q7,Q11:Q15,Q17,Q19)</f>
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="16:21" x14ac:dyDescent="0.35">
+    <row r="22" spans="16:21" x14ac:dyDescent="0.25">
       <c r="P22" s="71" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="23" spans="16:21" x14ac:dyDescent="0.35">
+    <row r="23" spans="16:21" x14ac:dyDescent="0.25">
       <c r="P23" t="s">
         <v>257</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>0.53533333333333433</v>
       </c>
     </row>
-    <row r="24" spans="16:21" x14ac:dyDescent="0.35">
+    <row r="24" spans="16:21" x14ac:dyDescent="0.25">
       <c r="P24" t="s">
         <v>258</v>
       </c>
@@ -10660,28 +10660,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9EEF34C-533F-4D76-B456-E79BEA524DCC}">
   <dimension ref="A1:AQ101"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.1796875" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2021</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>199</v>
       </c>
@@ -10868,7 +10868,7 @@
         <v>1213309.5172925084</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>470</v>
       </c>
@@ -10963,7 +10963,7 @@
         <v>546510.48924034019</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>205</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>2090069.7248419826</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>209</v>
       </c>
@@ -11153,12 +11153,12 @@
         <v>1406155.6987444595</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>2021</v>
       </c>
@@ -11250,7 +11250,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>199</v>
       </c>
@@ -11345,7 +11345,7 @@
         <v>2392614.7852066685</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>470</v>
       </c>
@@ -11440,7 +11440,7 @@
         <v>834725.65369765111</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>205</v>
       </c>
@@ -11535,7 +11535,7 @@
         <v>7911207.6996868448</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>209</v>
       </c>
@@ -11630,17 +11630,17 @@
         <v>2772902.4351726989</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>2021</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>199</v>
       </c>
@@ -11677,7 +11677,7 @@
       <c r="AD20" s="124"/>
       <c r="AE20" s="124"/>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>470</v>
       </c>
@@ -11714,7 +11714,7 @@
       <c r="AD21" s="124"/>
       <c r="AE21" s="124"/>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>205</v>
       </c>
@@ -11751,7 +11751,7 @@
       <c r="AD22" s="124"/>
       <c r="AE22" s="124"/>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>209</v>
       </c>
@@ -11788,17 +11788,17 @@
       <c r="AD23" s="124"/>
       <c r="AE23" s="124"/>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>199</v>
       </c>
@@ -11806,7 +11806,7 @@
         <v>65750.800457615216</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>470</v>
       </c>
@@ -11814,7 +11814,7 @@
         <v>26096.967191940064</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>205</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>133213.1552570395</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>209</v>
       </c>
@@ -11830,17 +11830,17 @@
         <v>65750.800457615216</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>2021</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>199</v>
       </c>
@@ -11877,7 +11877,7 @@
       <c r="AD34" s="124"/>
       <c r="AE34" s="124"/>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>470</v>
       </c>
@@ -11914,7 +11914,7 @@
       <c r="AD35" s="124"/>
       <c r="AE35" s="124"/>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>205</v>
       </c>
@@ -11951,7 +11951,7 @@
       <c r="AD36" s="124"/>
       <c r="AE36" s="124"/>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>209</v>
       </c>
@@ -11988,17 +11988,17 @@
       <c r="AD37" s="124"/>
       <c r="AE37" s="124"/>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B40">
         <v>2021</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>199</v>
       </c>
@@ -12007,7 +12007,7 @@
         <v>7.1681929364874337</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>470</v>
       </c>
@@ -12016,7 +12016,7 @@
         <v>1.6607160940325494</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>205</v>
       </c>
@@ -12025,7 +12025,7 @@
         <v>4.2704128132265557</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>209</v>
       </c>
@@ -12034,15 +12034,15 @@
         <v>12.14376215122577</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B45" s="124"/>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>487</v>
       </c>
@@ -12050,7 +12050,7 @@
         <v>91.94</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>488</v>
       </c>
@@ -12058,7 +12058,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>489</v>
       </c>
@@ -12066,12 +12066,12 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>491</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>492</v>
       </c>
@@ -12093,7 +12093,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>493</v>
       </c>
@@ -12104,7 +12104,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>494</v>
       </c>
@@ -12115,7 +12115,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>65</v>
       </c>
@@ -12126,12 +12126,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59" s="126"/>
       <c r="B59" s="110" t="s">
         <v>163</v>
@@ -12260,7 +12260,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>199</v>
       </c>
@@ -12433,7 +12433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>470</v>
       </c>
@@ -12606,7 +12606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>205</v>
       </c>
@@ -12779,7 +12779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>209</v>
       </c>
@@ -12952,20 +12952,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B64" s="128"/>
     </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A67" s="126"/>
       <c r="B67" s="110" t="s">
         <v>163</v>
@@ -13094,7 +13094,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>199</v>
       </c>
@@ -13147,7 +13147,7 @@
       <c r="AP68" s="129"/>
       <c r="AQ68" s="129"/>
     </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>470</v>
       </c>
@@ -13200,7 +13200,7 @@
       <c r="AP69" s="129"/>
       <c r="AQ69" s="129"/>
     </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>205</v>
       </c>
@@ -13253,7 +13253,7 @@
       <c r="AP70" s="129"/>
       <c r="AQ70" s="129"/>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>209</v>
       </c>
@@ -13306,12 +13306,12 @@
       <c r="AP71" s="129"/>
       <c r="AQ71" s="129"/>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A74" s="126"/>
       <c r="B74" s="110" t="s">
         <v>163</v>
@@ -13440,7 +13440,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>199</v>
       </c>
@@ -13613,7 +13613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>470</v>
       </c>
@@ -13786,7 +13786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>205</v>
       </c>
@@ -13959,7 +13959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>209</v>
       </c>
@@ -14132,7 +14132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B79" s="128"/>
       <c r="C79" s="128"/>
       <c r="D79" s="128"/>
@@ -14176,17 +14176,17 @@
       <c r="AP79" s="128"/>
       <c r="AQ79" s="128"/>
     </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A82" s="126"/>
       <c r="B82" s="110" t="s">
         <v>163</v>
@@ -14315,7 +14315,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>199</v>
       </c>
@@ -14365,7 +14365,7 @@
       <c r="AP83" s="129"/>
       <c r="AQ83" s="129"/>
     </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>470</v>
       </c>
@@ -14415,7 +14415,7 @@
       <c r="AP84" s="129"/>
       <c r="AQ84" s="129"/>
     </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>205</v>
       </c>
@@ -14465,7 +14465,7 @@
       <c r="AP85" s="129"/>
       <c r="AQ85" s="129"/>
     </row>
-    <row r="86" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>209</v>
       </c>
@@ -14515,12 +14515,12 @@
       <c r="AP86" s="129"/>
       <c r="AQ86" s="129"/>
     </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A89" s="126"/>
       <c r="B89" s="110" t="s">
         <v>163</v>
@@ -14649,7 +14649,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>199</v>
       </c>
@@ -14822,7 +14822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>470</v>
       </c>
@@ -14995,7 +14995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>205</v>
       </c>
@@ -15168,7 +15168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>209</v>
       </c>
@@ -15341,20 +15341,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B94" s="128"/>
     </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="97" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A97" s="126"/>
       <c r="B97" s="110" t="s">
         <v>163</v>
@@ -15483,7 +15483,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>199</v>
       </c>
@@ -15533,7 +15533,7 @@
       <c r="AP98" s="129"/>
       <c r="AQ98" s="129"/>
     </row>
-    <row r="99" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>470</v>
       </c>
@@ -15583,7 +15583,7 @@
       <c r="AP99" s="129"/>
       <c r="AQ99" s="129"/>
     </row>
-    <row r="100" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>205</v>
       </c>
@@ -15633,7 +15633,7 @@
       <c r="AP100" s="129"/>
       <c r="AQ100" s="129"/>
     </row>
-    <row r="101" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>209</v>
       </c>
@@ -15694,33 +15694,33 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AS25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.54296875" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7265625" customWidth="1"/>
-    <col min="5" max="5" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7265625" customWidth="1"/>
-    <col min="14" max="24" width="7.7265625" customWidth="1"/>
-    <col min="25" max="26" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="9.7265625" customWidth="1"/>
-    <col min="29" max="33" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="41" max="43" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="24" width="7.7109375" customWidth="1"/>
+    <col min="25" max="26" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="9.7109375" customWidth="1"/>
+    <col min="29" max="33" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="43" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" s="126" t="s">
         <v>471</v>
       </c>
@@ -15851,7 +15851,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>199</v>
       </c>
@@ -16024,7 +16024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>469</v>
       </c>
@@ -16197,7 +16197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>470</v>
       </c>
@@ -16370,7 +16370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>200</v>
       </c>
@@ -16543,7 +16543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>201</v>
       </c>
@@ -16716,7 +16716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>202</v>
       </c>
@@ -16889,7 +16889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>203</v>
       </c>
@@ -17062,7 +17062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>204</v>
       </c>
@@ -17235,7 +17235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>205</v>
       </c>
@@ -17408,7 +17408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>206</v>
       </c>
@@ -17581,7 +17581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>207</v>
       </c>
@@ -17754,7 +17754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>208</v>
       </c>
@@ -17927,7 +17927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>209</v>
       </c>
@@ -18100,7 +18100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>210</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>211</v>
       </c>
@@ -18446,7 +18446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>212</v>
       </c>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>213</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>472</v>
       </c>
@@ -18966,7 +18966,7 @@
       </c>
       <c r="AS19" s="77"/>
     </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>473</v>
       </c>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="AS20" s="77"/>
     </row>
-    <row r="21" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>474</v>
       </c>
@@ -19314,7 +19314,7 @@
       </c>
       <c r="AS21" s="77"/>
     </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>475</v>
       </c>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="AS22" s="77"/>
     </row>
-    <row r="23" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>476</v>
       </c>
@@ -19661,7 +19661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A24" s="130" t="s">
         <v>511</v>
       </c>
@@ -19834,7 +19834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A25" s="130" t="s">
         <v>512</v>
       </c>
@@ -20019,32 +20019,32 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.453125" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7265625" customWidth="1"/>
-    <col min="5" max="5" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.1796875" customWidth="1"/>
-    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="24" width="8" customWidth="1"/>
-    <col min="25" max="26" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="9.7265625" customWidth="1"/>
-    <col min="29" max="33" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="7.1796875" customWidth="1"/>
-    <col min="41" max="43" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="9.7109375" customWidth="1"/>
+    <col min="29" max="33" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="7.140625" customWidth="1"/>
+    <col min="41" max="43" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" s="127" t="s">
         <v>471</v>
       </c>
@@ -20175,7 +20175,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>199</v>
       </c>
@@ -20348,7 +20348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>469</v>
       </c>
@@ -20521,7 +20521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>470</v>
       </c>
@@ -20694,7 +20694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>200</v>
       </c>
@@ -20867,7 +20867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>201</v>
       </c>
@@ -21040,7 +21040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>202</v>
       </c>
@@ -21213,7 +21213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>203</v>
       </c>
@@ -21386,7 +21386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>204</v>
       </c>
@@ -21559,7 +21559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>205</v>
       </c>
@@ -21732,7 +21732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>206</v>
       </c>
@@ -21905,7 +21905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>207</v>
       </c>
@@ -22078,7 +22078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>208</v>
       </c>
@@ -22251,7 +22251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>209</v>
       </c>
@@ -22424,7 +22424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>210</v>
       </c>
@@ -22597,7 +22597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>211</v>
       </c>
@@ -22770,7 +22770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>212</v>
       </c>
@@ -22943,7 +22943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>213</v>
       </c>
@@ -23116,7 +23116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>472</v>
       </c>
@@ -23289,7 +23289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>473</v>
       </c>
@@ -23462,7 +23462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>474</v>
       </c>
@@ -23635,7 +23635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>475</v>
       </c>
@@ -23808,7 +23808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>476</v>
       </c>
@@ -23981,7 +23981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" s="130" t="s">
         <v>511</v>
       </c>
@@ -24154,7 +24154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" s="130" t="s">
         <v>512</v>
       </c>
@@ -24338,32 +24338,32 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.453125" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7265625" customWidth="1"/>
-    <col min="5" max="5" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="24" width="8.26953125" customWidth="1"/>
-    <col min="25" max="26" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="9.7265625" customWidth="1"/>
-    <col min="29" max="33" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="41" max="43" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="24" width="8.28515625" customWidth="1"/>
+    <col min="25" max="26" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="9.7109375" customWidth="1"/>
+    <col min="29" max="33" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="43" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" s="127" t="s">
         <v>471</v>
       </c>
@@ -24494,7 +24494,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>199</v>
       </c>
@@ -24667,7 +24667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>469</v>
       </c>
@@ -24840,7 +24840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>470</v>
       </c>
@@ -25013,7 +25013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>200</v>
       </c>
@@ -25186,7 +25186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>201</v>
       </c>
@@ -25359,7 +25359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>202</v>
       </c>
@@ -25490,7 +25490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>203</v>
       </c>
@@ -25621,7 +25621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>204</v>
       </c>
@@ -25752,7 +25752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>205</v>
       </c>
@@ -25925,7 +25925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>206</v>
       </c>
@@ -26098,7 +26098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>207</v>
       </c>
@@ -26271,7 +26271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>208</v>
       </c>
@@ -26444,7 +26444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>209</v>
       </c>
@@ -26617,7 +26617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>210</v>
       </c>
@@ -26748,7 +26748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>211</v>
       </c>
@@ -26921,7 +26921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>212</v>
       </c>
@@ -27094,7 +27094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>213</v>
       </c>
@@ -27267,7 +27267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>472</v>
       </c>
@@ -27440,7 +27440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>473</v>
       </c>
@@ -27613,7 +27613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>474</v>
       </c>
@@ -27786,7 +27786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>475</v>
       </c>
@@ -27959,7 +27959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>476</v>
       </c>
@@ -28132,7 +28132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" s="130" t="s">
         <v>511</v>
       </c>
@@ -28305,7 +28305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" s="130" t="s">
         <v>512</v>
       </c>
